--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5542BCF-04DF-4D53-965D-FBA38BA20048}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73E3B63-A710-4F44-B981-E7145D6D9F6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -292,6 +292,26 @@
   </si>
   <si>
     <t>これからのやつ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>欠席</t>
+    <rPh sb="0" eb="2">
+      <t>ケッセキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>予定有、いない場合</t>
+    <rPh sb="0" eb="2">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
     <phoneticPr fontId="19"/>
   </si>
 </sst>
@@ -557,7 +577,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -839,6 +859,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="59">
     <border>
@@ -1688,7 +1714,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1981,27 +2007,6 @@
     <xf numFmtId="0" fontId="24" fillId="46" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="39" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="39" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="39" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="34" fillId="43" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2059,6 +2064,26 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="49" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="50" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="50" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="39" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="39" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="27" fillId="39" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2117,25 +2142,11 @@
     <cellStyle name="名前" xfId="11" xr:uid="{B2D3C1EE-6B41-4801-AAFC-C2274E49E503}"/>
     <cellStyle name="良い" xfId="18" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="76">
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2156,98 +2167,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2303,28 +2223,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2359,217 +2258,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2683,15 +2372,15 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="作業リスト" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="75"/>
-      <tableStyleElement type="headerRow" dxfId="74"/>
-      <tableStyleElement type="totalRow" dxfId="73"/>
-      <tableStyleElement type="firstColumn" dxfId="72"/>
-      <tableStyleElement type="lastColumn" dxfId="71"/>
-      <tableStyleElement type="firstRowStripe" dxfId="70"/>
-      <tableStyleElement type="secondRowStripe" dxfId="69"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="68"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="67"/>
+      <tableStyleElement type="wholeTable" dxfId="27"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="firstColumn" dxfId="24"/>
+      <tableStyleElement type="lastColumn" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="20"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="19"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3060,7 +2749,7 @@
     <col min="4" max="4" width="12.6640625" style="9" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" style="6" customWidth="1"/>
     <col min="6" max="47" width="5.21875" style="6" customWidth="1"/>
-    <col min="48" max="48" width="11.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.77734375" style="6" customWidth="1"/>
     <col min="49" max="68" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="69" max="16384" width="8.77734375" style="6"/>
   </cols>
@@ -3081,11 +2770,11 @@
         <v>35</v>
       </c>
       <c r="F2" s="10"/>
-      <c r="I2" s="119"/>
+      <c r="I2" s="112"/>
       <c r="J2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="126"/>
+      <c r="M2" s="119"/>
       <c r="N2" s="6" t="s">
         <v>37</v>
       </c>
@@ -3100,8 +2789,8 @@
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
     </row>
     <row r="5" spans="1:68" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -3113,66 +2802,66 @@
       <c r="C5" s="15"/>
       <c r="D5" s="55"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="110">
+      <c r="F5" s="132">
         <f>D10</f>
         <v>46273</v>
       </c>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="112"/>
-      <c r="M5" s="110">
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="132">
         <f>M6</f>
         <v>46280</v>
       </c>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="113">
+      <c r="N5" s="133"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="133"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="135">
         <f>T6</f>
         <v>46287</v>
       </c>
-      <c r="U5" s="111"/>
-      <c r="V5" s="111"/>
-      <c r="W5" s="111"/>
-      <c r="X5" s="111"/>
-      <c r="Y5" s="111"/>
-      <c r="Z5" s="114"/>
-      <c r="AA5" s="110">
+      <c r="U5" s="133"/>
+      <c r="V5" s="133"/>
+      <c r="W5" s="133"/>
+      <c r="X5" s="133"/>
+      <c r="Y5" s="133"/>
+      <c r="Z5" s="136"/>
+      <c r="AA5" s="132">
         <f>AA6</f>
         <v>46294</v>
       </c>
-      <c r="AB5" s="111"/>
-      <c r="AC5" s="111"/>
-      <c r="AD5" s="111"/>
-      <c r="AE5" s="111"/>
-      <c r="AF5" s="111"/>
-      <c r="AG5" s="112"/>
-      <c r="AH5" s="113">
+      <c r="AB5" s="133"/>
+      <c r="AC5" s="133"/>
+      <c r="AD5" s="133"/>
+      <c r="AE5" s="133"/>
+      <c r="AF5" s="133"/>
+      <c r="AG5" s="134"/>
+      <c r="AH5" s="135">
         <f>AH6</f>
         <v>46301</v>
       </c>
-      <c r="AI5" s="111"/>
-      <c r="AJ5" s="111"/>
-      <c r="AK5" s="111"/>
-      <c r="AL5" s="111"/>
-      <c r="AM5" s="111"/>
-      <c r="AN5" s="114"/>
-      <c r="AO5" s="110">
+      <c r="AI5" s="133"/>
+      <c r="AJ5" s="133"/>
+      <c r="AK5" s="133"/>
+      <c r="AL5" s="133"/>
+      <c r="AM5" s="133"/>
+      <c r="AN5" s="136"/>
+      <c r="AO5" s="132">
         <f>AO6</f>
         <v>46308</v>
       </c>
-      <c r="AP5" s="111"/>
-      <c r="AQ5" s="111"/>
-      <c r="AR5" s="111"/>
-      <c r="AS5" s="111"/>
-      <c r="AT5" s="111"/>
-      <c r="AU5" s="112"/>
+      <c r="AP5" s="133"/>
+      <c r="AQ5" s="133"/>
+      <c r="AR5" s="133"/>
+      <c r="AS5" s="133"/>
+      <c r="AT5" s="133"/>
+      <c r="AU5" s="134"/>
       <c r="AV5" s="101" t="s">
         <v>24</v>
       </c>
@@ -3242,7 +2931,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="F6" s="127">
+      <c r="F6" s="120">
         <f>F5</f>
         <v>46273</v>
       </c>
@@ -3254,7 +2943,7 @@
         <f t="shared" ref="H6:AN6" si="0">G6+1</f>
         <v>46275</v>
       </c>
-      <c r="I6" s="129">
+      <c r="I6" s="122">
         <f t="shared" si="0"/>
         <v>46276</v>
       </c>
@@ -3266,11 +2955,11 @@
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
-      <c r="L6" s="131">
+      <c r="L6" s="124">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="M6" s="127">
+      <c r="M6" s="120">
         <f>L6+1</f>
         <v>46280</v>
       </c>
@@ -3278,11 +2967,11 @@
         <f>M6+1</f>
         <v>46281</v>
       </c>
-      <c r="O6" s="129">
+      <c r="O6" s="122">
         <f t="shared" si="0"/>
         <v>46282</v>
       </c>
-      <c r="P6" s="129">
+      <c r="P6" s="122">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
@@ -3294,7 +2983,7 @@
         <f t="shared" si="0"/>
         <v>46285</v>
       </c>
-      <c r="S6" s="120">
+      <c r="S6" s="113">
         <f t="shared" si="0"/>
         <v>46286</v>
       </c>
@@ -3306,11 +2995,11 @@
         <f>T6+1</f>
         <v>46288</v>
       </c>
-      <c r="V6" s="129">
+      <c r="V6" s="122">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-      <c r="W6" s="129">
+      <c r="W6" s="122">
         <f t="shared" si="0"/>
         <v>46290</v>
       </c>
@@ -3322,23 +3011,23 @@
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="Z6" s="133">
+      <c r="Z6" s="126">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="AA6" s="127">
+      <c r="AA6" s="120">
         <f>Z6+1</f>
         <v>46294</v>
       </c>
-      <c r="AB6" s="129">
+      <c r="AB6" s="122">
         <f>AA6+1</f>
         <v>46295</v>
       </c>
-      <c r="AC6" s="129">
+      <c r="AC6" s="122">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="AD6" s="129">
+      <c r="AD6" s="122">
         <f t="shared" si="0"/>
         <v>46297</v>
       </c>
@@ -3350,19 +3039,19 @@
         <f t="shared" si="0"/>
         <v>46299</v>
       </c>
-      <c r="AG6" s="131">
+      <c r="AG6" s="124">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="AH6" s="135">
+      <c r="AH6" s="128">
         <f>AG6+1</f>
         <v>46301</v>
       </c>
-      <c r="AI6" s="129">
+      <c r="AI6" s="122">
         <f>AH6+1</f>
         <v>46302</v>
       </c>
-      <c r="AJ6" s="129">
+      <c r="AJ6" s="122">
         <f t="shared" si="0"/>
         <v>46303</v>
       </c>
@@ -3382,19 +3071,19 @@
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="AO6" s="127">
+      <c r="AO6" s="120">
         <f>AN6+1</f>
         <v>46308</v>
       </c>
-      <c r="AP6" s="129">
+      <c r="AP6" s="122">
         <f>AO6+1</f>
         <v>46309</v>
       </c>
-      <c r="AQ6" s="129">
+      <c r="AQ6" s="122">
         <f t="shared" ref="AQ6" si="1">AP6+1</f>
         <v>46310</v>
       </c>
-      <c r="AR6" s="129">
+      <c r="AR6" s="122">
         <f t="shared" ref="AR6" si="2">AQ6+1</f>
         <v>46311</v>
       </c>
@@ -3413,8 +3102,12 @@
       <c r="AV6" s="102">
         <v>46279</v>
       </c>
-      <c r="AW6" s="102"/>
-      <c r="AX6" s="102"/>
+      <c r="AW6" s="102">
+        <v>46280</v>
+      </c>
+      <c r="AX6" s="102">
+        <v>46282</v>
+      </c>
       <c r="AY6" s="102"/>
       <c r="AZ6" s="102"/>
       <c r="BA6" s="102"/>
@@ -3450,7 +3143,7 @@
       <c r="E7" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="128" t="str">
+      <c r="F7" s="121" t="str">
         <f t="shared" ref="F7:AK7" si="6">LEFT(TEXT(F6,"aaa"),1)</f>
         <v>火</v>
       </c>
@@ -3462,7 +3155,7 @@
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="I7" s="130" t="str">
+      <c r="I7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3470,15 +3163,15 @@
         <f t="shared" si="6"/>
         <v>土</v>
       </c>
-      <c r="K7" s="124" t="str">
+      <c r="K7" s="117" t="str">
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="L7" s="132" t="str">
+      <c r="L7" s="125" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="M7" s="128" t="str">
+      <c r="M7" s="121" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
@@ -3486,11 +3179,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="O7" s="130" t="str">
+      <c r="O7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="P7" s="130" t="str">
+      <c r="P7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3498,11 +3191,11 @@
         <f t="shared" si="6"/>
         <v>土</v>
       </c>
-      <c r="R7" s="125" t="str">
+      <c r="R7" s="118" t="str">
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="S7" s="121" t="str">
+      <c r="S7" s="114" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
@@ -3514,11 +3207,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="V7" s="130" t="str">
+      <c r="V7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="W7" s="130" t="str">
+      <c r="W7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3526,27 +3219,27 @@
         <f t="shared" si="6"/>
         <v>土</v>
       </c>
-      <c r="Y7" s="125" t="str">
+      <c r="Y7" s="118" t="str">
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="Z7" s="134" t="str">
+      <c r="Z7" s="127" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AA7" s="128" t="str">
+      <c r="AA7" s="121" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AB7" s="130" t="str">
+      <c r="AB7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AC7" s="130" t="str">
+      <c r="AC7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="AD7" s="130" t="str">
+      <c r="AD7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3554,23 +3247,23 @@
         <f t="shared" si="6"/>
         <v>土</v>
       </c>
-      <c r="AF7" s="125" t="str">
+      <c r="AF7" s="118" t="str">
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="AG7" s="132" t="str">
+      <c r="AG7" s="125" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AH7" s="136" t="str">
+      <c r="AH7" s="129" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AI7" s="130" t="str">
+      <c r="AI7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AJ7" s="130" t="str">
+      <c r="AJ7" s="123" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
@@ -3582,27 +3275,27 @@
         <f t="shared" ref="AL7:AR7" si="7">LEFT(TEXT(AL6,"aaa"),1)</f>
         <v>土</v>
       </c>
-      <c r="AM7" s="125" t="str">
+      <c r="AM7" s="118" t="str">
         <f t="shared" si="7"/>
         <v>日</v>
       </c>
-      <c r="AN7" s="122" t="str">
+      <c r="AN7" s="115" t="str">
         <f t="shared" si="7"/>
         <v>月</v>
       </c>
-      <c r="AO7" s="128" t="str">
+      <c r="AO7" s="121" t="str">
         <f t="shared" si="7"/>
         <v>火</v>
       </c>
-      <c r="AP7" s="130" t="str">
+      <c r="AP7" s="123" t="str">
         <f t="shared" si="7"/>
         <v>水</v>
       </c>
-      <c r="AQ7" s="130" t="str">
+      <c r="AQ7" s="123" t="str">
         <f t="shared" si="7"/>
         <v>木</v>
       </c>
-      <c r="AR7" s="130" t="str">
+      <c r="AR7" s="123" t="str">
         <f t="shared" si="7"/>
         <v>金</v>
       </c>
@@ -3610,11 +3303,11 @@
         <f t="shared" ref="AS7:AU7" si="8">LEFT(TEXT(AS6,"aaa"),1)</f>
         <v>土</v>
       </c>
-      <c r="AT7" s="125" t="str">
+      <c r="AT7" s="118" t="str">
         <f t="shared" si="8"/>
         <v>日</v>
       </c>
-      <c r="AU7" s="123" t="str">
+      <c r="AU7" s="116" t="str">
         <f t="shared" si="8"/>
         <v>月</v>
       </c>
@@ -3844,16 +3537,16 @@
       <c r="E10" s="52">
         <v>46279</v>
       </c>
-      <c r="F10" s="118"/>
+      <c r="F10" s="111"/>
       <c r="G10" s="71"/>
       <c r="H10" s="71"/>
-      <c r="I10" s="119"/>
+      <c r="I10" s="112"/>
       <c r="J10" s="71"/>
       <c r="K10" s="71"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="116"/>
+      <c r="L10" s="112"/>
+      <c r="M10" s="112"/>
       <c r="N10" s="71"/>
-      <c r="O10" s="71"/>
+      <c r="O10" s="112"/>
       <c r="P10" s="71"/>
       <c r="Q10" s="71"/>
       <c r="R10" s="71"/>
@@ -3889,8 +3582,12 @@
       <c r="AV10" s="99">
         <v>1</v>
       </c>
-      <c r="AW10" s="99"/>
-      <c r="AX10" s="99"/>
+      <c r="AW10" s="99">
+        <v>0.95</v>
+      </c>
+      <c r="AX10" s="99">
+        <v>1</v>
+      </c>
       <c r="AY10" s="99"/>
       <c r="AZ10" s="99"/>
       <c r="BA10" s="99"/>
@@ -3932,10 +3629,10 @@
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
-      <c r="L11" s="119"/>
-      <c r="M11" s="126"/>
+      <c r="L11" s="112"/>
+      <c r="M11" s="112"/>
       <c r="N11" s="71"/>
-      <c r="O11" s="126"/>
+      <c r="O11" s="112"/>
       <c r="P11" s="71"/>
       <c r="Q11" s="71"/>
       <c r="R11" s="71"/>
@@ -3971,8 +3668,12 @@
       <c r="AV11" s="99">
         <v>0.6</v>
       </c>
-      <c r="AW11" s="99"/>
-      <c r="AX11" s="99"/>
+      <c r="AW11" s="99">
+        <v>0.2</v>
+      </c>
+      <c r="AX11" s="99">
+        <v>0.7</v>
+      </c>
       <c r="AY11" s="99"/>
       <c r="AZ11" s="99"/>
       <c r="BA11" s="99"/>
@@ -4015,18 +3716,18 @@
       <c r="L12" s="72"/>
       <c r="M12" s="72"/>
       <c r="N12" s="71"/>
-      <c r="O12" s="126"/>
-      <c r="P12" s="126"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="119"/>
       <c r="Q12" s="71"/>
       <c r="R12" s="71"/>
       <c r="S12" s="85"/>
       <c r="T12" s="77"/>
       <c r="U12" s="71"/>
-      <c r="V12" s="126"/>
-      <c r="W12" s="126"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="119"/>
       <c r="X12" s="71"/>
       <c r="Y12" s="71"/>
-      <c r="Z12" s="126"/>
+      <c r="Z12" s="119"/>
       <c r="AA12" s="70"/>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
@@ -4052,7 +3753,9 @@
         <v>0</v>
       </c>
       <c r="AW12" s="98"/>
-      <c r="AX12" s="98"/>
+      <c r="AX12" s="99">
+        <v>0</v>
+      </c>
       <c r="AY12" s="98"/>
       <c r="AZ12" s="98"/>
       <c r="BA12" s="98"/>
@@ -4277,8 +3980,12 @@
       <c r="AV15" s="99">
         <v>0</v>
       </c>
-      <c r="AW15" s="98"/>
-      <c r="AX15" s="98"/>
+      <c r="AW15" s="99">
+        <v>0</v>
+      </c>
+      <c r="AX15" s="99">
+        <v>0</v>
+      </c>
       <c r="AY15" s="98"/>
       <c r="AZ15" s="98"/>
       <c r="BA15" s="98"/>
@@ -4357,8 +4064,12 @@
       <c r="AV16" s="99">
         <v>0</v>
       </c>
-      <c r="AW16" s="98"/>
-      <c r="AX16" s="98"/>
+      <c r="AW16" s="99">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="99">
+        <v>0</v>
+      </c>
       <c r="AY16" s="98"/>
       <c r="AZ16" s="98"/>
       <c r="BA16" s="98"/>
@@ -4437,8 +4148,12 @@
       <c r="AV17" s="99">
         <v>0</v>
       </c>
-      <c r="AW17" s="98"/>
-      <c r="AX17" s="98"/>
+      <c r="AW17" s="99">
+        <v>0</v>
+      </c>
+      <c r="AX17" s="99">
+        <v>0</v>
+      </c>
       <c r="AY17" s="98"/>
       <c r="AZ17" s="98"/>
       <c r="BA17" s="98"/>
@@ -4531,9 +4246,15 @@
       <c r="BP18" s="100"/>
     </row>
     <row r="20" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="117"/>
+      <c r="B20" s="110"/>
       <c r="C20" s="12"/>
       <c r="E20" s="13"/>
+    </row>
+    <row r="21" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="130"/>
+      <c r="H21" s="6" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="22" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E22" s="14" t="s">
@@ -4598,9 +4319,13 @@
       <c r="J24" s="105"/>
       <c r="K24" s="105"/>
       <c r="L24" s="104"/>
-      <c r="M24" s="104"/>
+      <c r="M24" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="N24" s="105"/>
-      <c r="O24" s="104"/>
+      <c r="O24" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="P24" s="104"/>
       <c r="Q24" s="105"/>
       <c r="R24" s="105"/>
@@ -4647,19 +4372,17 @@
       <c r="L25" s="104"/>
       <c r="M25" s="104"/>
       <c r="N25" s="105"/>
-      <c r="O25" s="104"/>
+      <c r="O25" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="P25" s="104"/>
       <c r="Q25" s="105"/>
       <c r="R25" s="105"/>
       <c r="S25" s="105"/>
       <c r="T25" s="105"/>
       <c r="U25" s="105"/>
-      <c r="V25" s="108" t="s">
-        <v>27</v>
-      </c>
-      <c r="W25" s="108" t="s">
-        <v>27</v>
-      </c>
+      <c r="V25" s="104"/>
+      <c r="W25" s="104"/>
       <c r="X25" s="105"/>
       <c r="Y25" s="105"/>
       <c r="Z25" s="108" t="s">
@@ -4786,7 +4509,9 @@
       <c r="Y27" s="105"/>
       <c r="Z27" s="104"/>
       <c r="AA27" s="104"/>
-      <c r="AB27" s="104"/>
+      <c r="AB27" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="AC27" s="104"/>
       <c r="AD27" s="104"/>
       <c r="AE27" s="105"/>
@@ -4828,7 +4553,9 @@
       <c r="T28" s="105"/>
       <c r="U28" s="105"/>
       <c r="V28" s="104"/>
-      <c r="W28" s="104"/>
+      <c r="W28" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="X28" s="105"/>
       <c r="Y28" s="105"/>
       <c r="Z28" s="104"/>
@@ -4867,55 +4594,55 @@
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F6:AU18">
-    <cfRule type="expression" dxfId="5" priority="25">
+    <cfRule type="expression" dxfId="18" priority="25">
       <formula>WEEKDAY(F$6,2)=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="26">
+    <cfRule type="expression" dxfId="17" priority="26">
       <formula>WEEKDAY(F$6,2)=7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G24:H28 J24:K28 N24:N28 Q24:U28 X24:Y28 AE24:AF28 AK24:AN28 AS23:AT28">
-    <cfRule type="expression" dxfId="24" priority="21">
+    <cfRule type="expression" dxfId="16" priority="21">
       <formula>WEEKDAY(G$6,2)=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="22">
+    <cfRule type="expression" dxfId="15" priority="22">
       <formula>WEEKDAY(G$6,2)=7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G23:H23 J23:K23 N23 Q23:U23 X23:Y23 AF23 AK23:AN23">
-    <cfRule type="expression" dxfId="22" priority="17">
+    <cfRule type="expression" dxfId="14" priority="17">
       <formula>WEEKDAY(G$6,2)=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="18">
+    <cfRule type="expression" dxfId="13" priority="18">
       <formula>WEEKDAY(G$6,2)=7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE23">
-    <cfRule type="expression" dxfId="18" priority="16">
+    <cfRule type="expression" dxfId="12" priority="16">
       <formula>AND(AE$6&gt;=$D23,AE$6&lt;=$E23)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE23">
-    <cfRule type="expression" dxfId="17" priority="13">
+    <cfRule type="expression" dxfId="11" priority="13">
       <formula>WEEKDAY(AE$6,2)=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="14">
+    <cfRule type="expression" dxfId="10" priority="14">
       <formula>WEEKDAY(AE$6,2)=7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="9" priority="10">
       <formula>WEEKDAY(I$6,2)=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>WEEKDAY(I$6,2)=7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>WEEKDAY(M$6,2)=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>WEEKDAY(M$6,2)=7</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5153,26 +4880,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5460,7 +5167,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5469,26 +5176,27 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5509,10 +5217,29 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73E3B63-A710-4F44-B981-E7145D6D9F6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DD7611-B2B2-4DB1-BEDC-3FF3BB456B33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13755" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -3108,8 +3108,12 @@
       <c r="AX6" s="102">
         <v>46282</v>
       </c>
-      <c r="AY6" s="102"/>
-      <c r="AZ6" s="102"/>
+      <c r="AY6" s="102">
+        <v>46283</v>
+      </c>
+      <c r="AZ6" s="102">
+        <v>46289</v>
+      </c>
       <c r="BA6" s="102"/>
       <c r="BB6" s="102"/>
       <c r="BC6" s="102"/>
@@ -3535,7 +3539,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="52">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="F10" s="111"/>
       <c r="G10" s="71"/>
@@ -3588,8 +3592,12 @@
       <c r="AX10" s="99">
         <v>1</v>
       </c>
-      <c r="AY10" s="99"/>
-      <c r="AZ10" s="99"/>
+      <c r="AY10" s="99">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="99">
+        <v>1</v>
+      </c>
       <c r="BA10" s="99"/>
       <c r="BB10" s="99"/>
       <c r="BC10" s="99"/>
@@ -3621,7 +3629,7 @@
         <v>46280</v>
       </c>
       <c r="E11" s="59">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -3633,13 +3641,13 @@
       <c r="M11" s="112"/>
       <c r="N11" s="71"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="71"/>
+      <c r="P11" s="112"/>
       <c r="Q11" s="71"/>
       <c r="R11" s="71"/>
       <c r="S11" s="85"/>
       <c r="T11" s="77"/>
       <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
+      <c r="V11" s="112"/>
       <c r="W11" s="71"/>
       <c r="X11" s="71"/>
       <c r="Y11" s="71"/>
@@ -3674,8 +3682,12 @@
       <c r="AX11" s="99">
         <v>0.7</v>
       </c>
-      <c r="AY11" s="99"/>
-      <c r="AZ11" s="99"/>
+      <c r="AY11" s="99">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="99">
+        <v>1</v>
+      </c>
       <c r="BA11" s="99"/>
       <c r="BB11" s="99"/>
       <c r="BC11" s="99"/>
@@ -3723,7 +3735,7 @@
       <c r="S12" s="85"/>
       <c r="T12" s="77"/>
       <c r="U12" s="71"/>
-      <c r="V12" s="119"/>
+      <c r="V12" s="112"/>
       <c r="W12" s="119"/>
       <c r="X12" s="71"/>
       <c r="Y12" s="71"/>
@@ -3756,8 +3768,12 @@
       <c r="AX12" s="99">
         <v>0</v>
       </c>
-      <c r="AY12" s="98"/>
-      <c r="AZ12" s="98"/>
+      <c r="AY12" s="99">
+        <v>0.05</v>
+      </c>
+      <c r="AZ12" s="99">
+        <v>0.15</v>
+      </c>
       <c r="BA12" s="98"/>
       <c r="BB12" s="98"/>
       <c r="BC12" s="98"/>
@@ -4326,7 +4342,9 @@
       <c r="O24" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="P24" s="104"/>
+      <c r="P24" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="Q24" s="105"/>
       <c r="R24" s="105"/>
       <c r="S24" s="105"/>
@@ -4375,7 +4393,9 @@
       <c r="O25" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="P25" s="104"/>
+      <c r="P25" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="Q25" s="105"/>
       <c r="R25" s="105"/>
       <c r="S25" s="105"/>
@@ -4503,7 +4523,9 @@
       <c r="S27" s="105"/>
       <c r="T27" s="105"/>
       <c r="U27" s="105"/>
-      <c r="V27" s="104"/>
+      <c r="V27" s="131" t="s">
+        <v>38</v>
+      </c>
       <c r="W27" s="104"/>
       <c r="X27" s="105"/>
       <c r="Y27" s="105"/>
@@ -4880,6 +4902,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5167,15 +5198,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5197,6 +5219,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5217,28 +5247,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73E3B63-A710-4F44-B981-E7145D6D9F6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F94A5E-39BB-4F1F-980B-C26BBB28B76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="11895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -30,8 +30,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>作成者</author>
+  </authors>
+  <commentList>
+    <comment ref="Z12" authorId="0" shapeId="0" xr:uid="{ED8264A6-3574-4C67-9311-B0156B135D83}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>作成者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+実装の予定をたてる</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -329,7 +365,7 @@
     <numFmt numFmtId="180" formatCode="d"/>
     <numFmt numFmtId="181" formatCode="yy/mm/dd;@"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +609,21 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -866,7 +917,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -1639,6 +1690,51 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1714,7 +1810,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2032,9 +2128,6 @@
     <xf numFmtId="0" fontId="31" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="29" fillId="49" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2067,6 +2160,24 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="50" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="50" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2451,13 +2562,13 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFC0C0C0"/>
+      <color rgb="FF969696"/>
       <color rgb="FFFFFF66"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FF215881"/>
       <color rgb="FF42648A"/>
-      <color rgb="FF969696"/>
-      <color rgb="FFC0C0C0"/>
       <color rgb="FF427FC2"/>
       <color rgb="FF44678E"/>
       <color rgb="FF4A6F9C"/>
@@ -2736,12 +2847,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP28"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="8" customWidth="1"/>
     <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
@@ -2754,7 +2865,7 @@
     <col min="69" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="21.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:68" ht="21.6" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -2762,7 +2873,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:68" ht="30" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -2774,25 +2885,25 @@
       <c r="J2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="119"/>
+      <c r="M2" s="132"/>
       <c r="N2" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:68" ht="10.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:68" ht="10.9" customHeight="1">
       <c r="B3" s="2"/>
       <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:68" ht="22.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:68" ht="22.9" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
     </row>
-    <row r="5" spans="1:68" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:68" ht="25.9" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2802,66 +2913,66 @@
       <c r="C5" s="15"/>
       <c r="D5" s="55"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="132">
+      <c r="F5" s="137">
         <f>D10</f>
         <v>46273</v>
       </c>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="132">
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="137">
         <f>M6</f>
         <v>46280</v>
       </c>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="133"/>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="135">
+      <c r="N5" s="138"/>
+      <c r="O5" s="138"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="138"/>
+      <c r="R5" s="138"/>
+      <c r="S5" s="139"/>
+      <c r="T5" s="140">
         <f>T6</f>
         <v>46287</v>
       </c>
-      <c r="U5" s="133"/>
-      <c r="V5" s="133"/>
-      <c r="W5" s="133"/>
-      <c r="X5" s="133"/>
-      <c r="Y5" s="133"/>
-      <c r="Z5" s="136"/>
-      <c r="AA5" s="132">
+      <c r="U5" s="138"/>
+      <c r="V5" s="138"/>
+      <c r="W5" s="138"/>
+      <c r="X5" s="138"/>
+      <c r="Y5" s="138"/>
+      <c r="Z5" s="141"/>
+      <c r="AA5" s="137">
         <f>AA6</f>
         <v>46294</v>
       </c>
-      <c r="AB5" s="133"/>
-      <c r="AC5" s="133"/>
-      <c r="AD5" s="133"/>
-      <c r="AE5" s="133"/>
-      <c r="AF5" s="133"/>
-      <c r="AG5" s="134"/>
-      <c r="AH5" s="135">
+      <c r="AB5" s="138"/>
+      <c r="AC5" s="138"/>
+      <c r="AD5" s="138"/>
+      <c r="AE5" s="138"/>
+      <c r="AF5" s="138"/>
+      <c r="AG5" s="139"/>
+      <c r="AH5" s="140">
         <f>AH6</f>
         <v>46301</v>
       </c>
-      <c r="AI5" s="133"/>
-      <c r="AJ5" s="133"/>
-      <c r="AK5" s="133"/>
-      <c r="AL5" s="133"/>
-      <c r="AM5" s="133"/>
-      <c r="AN5" s="136"/>
-      <c r="AO5" s="132">
+      <c r="AI5" s="138"/>
+      <c r="AJ5" s="138"/>
+      <c r="AK5" s="138"/>
+      <c r="AL5" s="138"/>
+      <c r="AM5" s="138"/>
+      <c r="AN5" s="141"/>
+      <c r="AO5" s="137">
         <f>AO6</f>
         <v>46308</v>
       </c>
-      <c r="AP5" s="133"/>
-      <c r="AQ5" s="133"/>
-      <c r="AR5" s="133"/>
-      <c r="AS5" s="133"/>
-      <c r="AT5" s="133"/>
-      <c r="AU5" s="134"/>
+      <c r="AP5" s="138"/>
+      <c r="AQ5" s="138"/>
+      <c r="AR5" s="138"/>
+      <c r="AS5" s="138"/>
+      <c r="AT5" s="138"/>
+      <c r="AU5" s="139"/>
       <c r="AV5" s="101" t="s">
         <v>24</v>
       </c>
@@ -2926,12 +3037,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" ht="21" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="F6" s="120">
+      <c r="F6" s="119">
         <f>F5</f>
         <v>46273</v>
       </c>
@@ -2943,7 +3054,7 @@
         <f t="shared" ref="H6:AN6" si="0">G6+1</f>
         <v>46275</v>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="121">
         <f t="shared" si="0"/>
         <v>46276</v>
       </c>
@@ -2955,11 +3066,11 @@
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
-      <c r="L6" s="124">
+      <c r="L6" s="123">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="M6" s="120">
+      <c r="M6" s="119">
         <f>L6+1</f>
         <v>46280</v>
       </c>
@@ -2967,11 +3078,11 @@
         <f>M6+1</f>
         <v>46281</v>
       </c>
-      <c r="O6" s="122">
+      <c r="O6" s="121">
         <f t="shared" si="0"/>
         <v>46282</v>
       </c>
-      <c r="P6" s="122">
+      <c r="P6" s="121">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
@@ -2995,11 +3106,11 @@
         <f>T6+1</f>
         <v>46288</v>
       </c>
-      <c r="V6" s="122">
+      <c r="V6" s="121">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-      <c r="W6" s="122">
+      <c r="W6" s="121">
         <f t="shared" si="0"/>
         <v>46290</v>
       </c>
@@ -3011,23 +3122,23 @@
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="Z6" s="126">
+      <c r="Z6" s="125">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="AA6" s="120">
+      <c r="AA6" s="119">
         <f>Z6+1</f>
         <v>46294</v>
       </c>
-      <c r="AB6" s="122">
+      <c r="AB6" s="121">
         <f>AA6+1</f>
         <v>46295</v>
       </c>
-      <c r="AC6" s="122">
+      <c r="AC6" s="121">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="AD6" s="122">
+      <c r="AD6" s="121">
         <f t="shared" si="0"/>
         <v>46297</v>
       </c>
@@ -3039,19 +3150,19 @@
         <f t="shared" si="0"/>
         <v>46299</v>
       </c>
-      <c r="AG6" s="124">
+      <c r="AG6" s="123">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="AH6" s="128">
+      <c r="AH6" s="127">
         <f>AG6+1</f>
         <v>46301</v>
       </c>
-      <c r="AI6" s="122">
+      <c r="AI6" s="121">
         <f>AH6+1</f>
         <v>46302</v>
       </c>
-      <c r="AJ6" s="122">
+      <c r="AJ6" s="121">
         <f t="shared" si="0"/>
         <v>46303</v>
       </c>
@@ -3071,19 +3182,19 @@
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="AO6" s="120">
+      <c r="AO6" s="119">
         <f>AN6+1</f>
         <v>46308</v>
       </c>
-      <c r="AP6" s="122">
+      <c r="AP6" s="121">
         <f>AO6+1</f>
         <v>46309</v>
       </c>
-      <c r="AQ6" s="122">
+      <c r="AQ6" s="121">
         <f t="shared" ref="AQ6" si="1">AP6+1</f>
         <v>46310</v>
       </c>
-      <c r="AR6" s="122">
+      <c r="AR6" s="121">
         <f t="shared" ref="AR6" si="2">AQ6+1</f>
         <v>46311</v>
       </c>
@@ -3108,9 +3219,15 @@
       <c r="AX6" s="102">
         <v>46282</v>
       </c>
-      <c r="AY6" s="102"/>
-      <c r="AZ6" s="102"/>
-      <c r="BA6" s="102"/>
+      <c r="AY6" s="102">
+        <v>46283</v>
+      </c>
+      <c r="AZ6" s="102">
+        <v>46289</v>
+      </c>
+      <c r="BA6" s="102">
+        <v>46290</v>
+      </c>
       <c r="BB6" s="102"/>
       <c r="BC6" s="102"/>
       <c r="BD6" s="102"/>
@@ -3127,7 +3244,7 @@
       <c r="BO6" s="102"/>
       <c r="BP6" s="102"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:68" ht="30" customHeight="1" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3143,7 +3260,7 @@
       <c r="E7" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="121" t="str">
+      <c r="F7" s="120" t="str">
         <f t="shared" ref="F7:AK7" si="6">LEFT(TEXT(F6,"aaa"),1)</f>
         <v>火</v>
       </c>
@@ -3155,7 +3272,7 @@
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="I7" s="123" t="str">
+      <c r="I7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3167,11 +3284,11 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="L7" s="125" t="str">
+      <c r="L7" s="124" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="M7" s="121" t="str">
+      <c r="M7" s="120" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
@@ -3179,11 +3296,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="O7" s="123" t="str">
+      <c r="O7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="P7" s="123" t="str">
+      <c r="P7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3207,11 +3324,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="V7" s="123" t="str">
+      <c r="V7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="W7" s="123" t="str">
+      <c r="W7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3223,23 +3340,23 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="Z7" s="127" t="str">
+      <c r="Z7" s="126" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AA7" s="121" t="str">
+      <c r="AA7" s="120" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AB7" s="123" t="str">
+      <c r="AB7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AC7" s="123" t="str">
+      <c r="AC7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="AD7" s="123" t="str">
+      <c r="AD7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3251,19 +3368,19 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="AG7" s="125" t="str">
+      <c r="AG7" s="124" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AH7" s="129" t="str">
+      <c r="AH7" s="128" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AI7" s="123" t="str">
+      <c r="AI7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AJ7" s="123" t="str">
+      <c r="AJ7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
@@ -3283,19 +3400,19 @@
         <f t="shared" si="7"/>
         <v>月</v>
       </c>
-      <c r="AO7" s="121" t="str">
+      <c r="AO7" s="120" t="str">
         <f t="shared" si="7"/>
         <v>火</v>
       </c>
-      <c r="AP7" s="123" t="str">
+      <c r="AP7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>水</v>
       </c>
-      <c r="AQ7" s="123" t="str">
+      <c r="AQ7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>木</v>
       </c>
-      <c r="AR7" s="123" t="str">
+      <c r="AR7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>金</v>
       </c>
@@ -3375,7 +3492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
@@ -3447,7 +3564,7 @@
       <c r="BO8" s="97"/>
       <c r="BP8" s="97"/>
     </row>
-    <row r="9" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -3521,7 +3638,7 @@
       <c r="BO9" s="98"/>
       <c r="BP9" s="98"/>
     </row>
-    <row r="10" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3535,7 +3652,7 @@
         <v>46273</v>
       </c>
       <c r="E10" s="52">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="F10" s="111"/>
       <c r="G10" s="71"/>
@@ -3543,8 +3660,8 @@
       <c r="I10" s="112"/>
       <c r="J10" s="71"/>
       <c r="K10" s="71"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
       <c r="N10" s="71"/>
       <c r="O10" s="112"/>
       <c r="P10" s="71"/>
@@ -3588,9 +3705,15 @@
       <c r="AX10" s="99">
         <v>1</v>
       </c>
-      <c r="AY10" s="99"/>
-      <c r="AZ10" s="99"/>
-      <c r="BA10" s="99"/>
+      <c r="AY10" s="99">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="99">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="99">
+        <v>1</v>
+      </c>
       <c r="BB10" s="99"/>
       <c r="BC10" s="99"/>
       <c r="BD10" s="99"/>
@@ -3607,7 +3730,7 @@
       <c r="BO10" s="99"/>
       <c r="BP10" s="99"/>
     </row>
-    <row r="11" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3621,7 +3744,7 @@
         <v>46280</v>
       </c>
       <c r="E11" s="59">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -3629,17 +3752,17 @@
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
       <c r="N11" s="71"/>
       <c r="O11" s="112"/>
-      <c r="P11" s="71"/>
+      <c r="P11" s="112"/>
       <c r="Q11" s="71"/>
       <c r="R11" s="71"/>
       <c r="S11" s="85"/>
       <c r="T11" s="77"/>
       <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
+      <c r="V11" s="112"/>
       <c r="W11" s="71"/>
       <c r="X11" s="71"/>
       <c r="Y11" s="71"/>
@@ -3674,9 +3797,15 @@
       <c r="AX11" s="99">
         <v>0.7</v>
       </c>
-      <c r="AY11" s="99"/>
-      <c r="AZ11" s="99"/>
-      <c r="BA11" s="99"/>
+      <c r="AY11" s="99">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="99">
+        <v>1</v>
+      </c>
+      <c r="BA11" s="99">
+        <v>1</v>
+      </c>
       <c r="BB11" s="99"/>
       <c r="BC11" s="99"/>
       <c r="BD11" s="99"/>
@@ -3693,7 +3822,7 @@
       <c r="BO11" s="99"/>
       <c r="BP11" s="99"/>
     </row>
-    <row r="12" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="51" t="s">
         <v>18</v>
@@ -3712,23 +3841,23 @@
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
       <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="119"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="132"/>
       <c r="Q12" s="71"/>
       <c r="R12" s="71"/>
       <c r="S12" s="85"/>
       <c r="T12" s="77"/>
-      <c r="U12" s="71"/>
-      <c r="V12" s="119"/>
-      <c r="W12" s="119"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="119"/>
-      <c r="AA12" s="70"/>
+      <c r="U12" s="86"/>
+      <c r="V12" s="112"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="77"/>
+      <c r="Y12" s="86"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="77"/>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
       <c r="AD12" s="71"/>
@@ -3756,9 +3885,15 @@
       <c r="AX12" s="99">
         <v>0</v>
       </c>
-      <c r="AY12" s="98"/>
-      <c r="AZ12" s="98"/>
-      <c r="BA12" s="98"/>
+      <c r="AY12" s="99">
+        <v>0.05</v>
+      </c>
+      <c r="AZ12" s="99">
+        <v>0.15</v>
+      </c>
+      <c r="BA12" s="99">
+        <v>0.2</v>
+      </c>
       <c r="BB12" s="98"/>
       <c r="BC12" s="98"/>
       <c r="BD12" s="98"/>
@@ -3775,7 +3910,7 @@
       <c r="BO12" s="98"/>
       <c r="BP12" s="98"/>
     </row>
-    <row r="13" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="56"/>
       <c r="C13" s="57" t="s">
@@ -3847,7 +3982,7 @@
       <c r="BO13" s="98"/>
       <c r="BP13" s="98"/>
     </row>
-    <row r="14" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -3921,7 +4056,7 @@
       <c r="BO14" s="98"/>
       <c r="BP14" s="98"/>
     </row>
-    <row r="15" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="53" t="s">
         <v>20</v>
@@ -4005,7 +4140,7 @@
       <c r="BO15" s="98"/>
       <c r="BP15" s="98"/>
     </row>
-    <row r="16" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="66" t="s">
         <v>21</v>
@@ -4089,7 +4224,7 @@
       <c r="BO16" s="98"/>
       <c r="BP16" s="98"/>
     </row>
-    <row r="17" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="53" t="s">
         <v>22</v>
@@ -4173,7 +4308,7 @@
       <c r="BO17" s="98"/>
       <c r="BP17" s="98"/>
     </row>
-    <row r="18" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="93"/>
       <c r="C18" s="94" t="s">
@@ -4245,23 +4380,23 @@
       <c r="BO18" s="100"/>
       <c r="BP18" s="100"/>
     </row>
-    <row r="20" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:68" ht="30" customHeight="1">
       <c r="B20" s="110"/>
       <c r="C20" s="12"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G21" s="130"/>
+    <row r="21" spans="1:68" ht="30" customHeight="1">
+      <c r="G21" s="129"/>
       <c r="H21" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:68" ht="30" customHeight="1">
       <c r="E22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:68" ht="30" customHeight="1">
       <c r="E23" s="106" t="s">
         <v>29</v>
       </c>
@@ -4308,7 +4443,7 @@
       <c r="AT23" s="109"/>
       <c r="AU23" s="104"/>
     </row>
-    <row r="24" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:68" ht="30" customHeight="1">
       <c r="E24" s="107" t="s">
         <v>30</v>
       </c>
@@ -4319,14 +4454,16 @@
       <c r="J24" s="105"/>
       <c r="K24" s="105"/>
       <c r="L24" s="104"/>
-      <c r="M24" s="131" t="s">
+      <c r="M24" s="130" t="s">
         <v>38</v>
       </c>
       <c r="N24" s="105"/>
-      <c r="O24" s="131" t="s">
+      <c r="O24" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="P24" s="104"/>
+      <c r="P24" s="130" t="s">
+        <v>38</v>
+      </c>
       <c r="Q24" s="105"/>
       <c r="R24" s="105"/>
       <c r="S24" s="105"/>
@@ -4359,7 +4496,7 @@
       <c r="AT24" s="105"/>
       <c r="AU24" s="104"/>
     </row>
-    <row r="25" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:68" ht="30" customHeight="1">
       <c r="E25" s="106" t="s">
         <v>31</v>
       </c>
@@ -4372,10 +4509,12 @@
       <c r="L25" s="104"/>
       <c r="M25" s="104"/>
       <c r="N25" s="105"/>
-      <c r="O25" s="131" t="s">
+      <c r="O25" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="P25" s="104"/>
+      <c r="P25" s="130" t="s">
+        <v>38</v>
+      </c>
       <c r="Q25" s="105"/>
       <c r="R25" s="105"/>
       <c r="S25" s="105"/>
@@ -4436,7 +4575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:68" ht="30" customHeight="1">
       <c r="E26" s="107" t="s">
         <v>32</v>
       </c>
@@ -4483,7 +4622,7 @@
       <c r="AT26" s="105"/>
       <c r="AU26" s="104"/>
     </row>
-    <row r="27" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:68" ht="30" customHeight="1">
       <c r="E27" s="106" t="s">
         <v>33</v>
       </c>
@@ -4503,13 +4642,15 @@
       <c r="S27" s="105"/>
       <c r="T27" s="105"/>
       <c r="U27" s="105"/>
-      <c r="V27" s="104"/>
+      <c r="V27" s="130" t="s">
+        <v>38</v>
+      </c>
       <c r="W27" s="104"/>
       <c r="X27" s="105"/>
       <c r="Y27" s="105"/>
       <c r="Z27" s="104"/>
       <c r="AA27" s="104"/>
-      <c r="AB27" s="131" t="s">
+      <c r="AB27" s="130" t="s">
         <v>38</v>
       </c>
       <c r="AC27" s="104"/>
@@ -4532,7 +4673,7 @@
       <c r="AT27" s="105"/>
       <c r="AU27" s="104"/>
     </row>
-    <row r="28" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:68" ht="30" customHeight="1">
       <c r="E28" s="107" t="s">
         <v>34</v>
       </c>
@@ -4553,7 +4694,7 @@
       <c r="T28" s="105"/>
       <c r="U28" s="105"/>
       <c r="V28" s="104"/>
-      <c r="W28" s="131" t="s">
+      <c r="W28" s="130" t="s">
         <v>38</v>
       </c>
       <c r="X28" s="105"/>
@@ -4657,6 +4798,7 @@
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4747,7 +4889,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781B8887-CE6A-4A0E-8262-8920C09EEF86}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4757,117 +4899,117 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE6A2FC-300A-4B2A-BCE2-26C39F90CFA2}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="82">
         <v>46023</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="82">
         <v>46034</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="82">
         <v>46064</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="82">
         <v>46076</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="82">
         <v>46101</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="82">
         <v>46141</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="82">
         <v>46145</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="82">
         <v>46146</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="82">
         <v>46147</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="82">
         <v>46223</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="82">
         <v>46245</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" s="82">
         <v>46274</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" s="82">
         <v>46275</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="82">
         <v>46281</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="82">
         <v>46286</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="82">
         <v>46287</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" s="82">
         <v>46288</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="82">
         <v>46304</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="82">
         <v>46307</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="82">
         <v>46329</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="82">
         <v>46349</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="82">
         <v>46379</v>
       </c>
@@ -4880,6 +5022,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5167,15 +5318,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5197,6 +5339,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5217,28 +5367,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DD7611-B2B2-4DB1-BEDC-3FF3BB456B33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F94A5E-39BB-4F1F-980B-C26BBB28B76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13755" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="11895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -28,6 +28,42 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>作成者</author>
+  </authors>
+  <commentList>
+    <comment ref="Z12" authorId="0" shapeId="0" xr:uid="{ED8264A6-3574-4C67-9311-B0156B135D83}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>作成者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+実装の予定をたてる</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -329,7 +365,7 @@
     <numFmt numFmtId="180" formatCode="d"/>
     <numFmt numFmtId="181" formatCode="yy/mm/dd;@"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +609,21 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -866,7 +917,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -1639,6 +1690,51 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1714,7 +1810,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2032,9 +2128,6 @@
     <xf numFmtId="0" fontId="31" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="29" fillId="49" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2067,6 +2160,24 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="50" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="50" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2451,13 +2562,13 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFC0C0C0"/>
+      <color rgb="FF969696"/>
       <color rgb="FFFFFF66"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FF215881"/>
       <color rgb="FF42648A"/>
-      <color rgb="FF969696"/>
-      <color rgb="FFC0C0C0"/>
       <color rgb="FF427FC2"/>
       <color rgb="FF44678E"/>
       <color rgb="FF4A6F9C"/>
@@ -2736,12 +2847,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP28"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="8" customWidth="1"/>
     <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
@@ -2754,7 +2865,7 @@
     <col min="69" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="21.6" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:68" ht="21.6" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -2762,7 +2873,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:68" ht="30" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -2774,25 +2885,25 @@
       <c r="J2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="119"/>
+      <c r="M2" s="132"/>
       <c r="N2" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:68" ht="10.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:68" ht="10.9" customHeight="1">
       <c r="B3" s="2"/>
       <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:68" ht="22.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:68" ht="22.9" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
     </row>
-    <row r="5" spans="1:68" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:68" ht="25.9" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2802,66 +2913,66 @@
       <c r="C5" s="15"/>
       <c r="D5" s="55"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="132">
+      <c r="F5" s="137">
         <f>D10</f>
         <v>46273</v>
       </c>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="132">
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="138"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="138"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="137">
         <f>M6</f>
         <v>46280</v>
       </c>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="133"/>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="135">
+      <c r="N5" s="138"/>
+      <c r="O5" s="138"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="138"/>
+      <c r="R5" s="138"/>
+      <c r="S5" s="139"/>
+      <c r="T5" s="140">
         <f>T6</f>
         <v>46287</v>
       </c>
-      <c r="U5" s="133"/>
-      <c r="V5" s="133"/>
-      <c r="W5" s="133"/>
-      <c r="X5" s="133"/>
-      <c r="Y5" s="133"/>
-      <c r="Z5" s="136"/>
-      <c r="AA5" s="132">
+      <c r="U5" s="138"/>
+      <c r="V5" s="138"/>
+      <c r="W5" s="138"/>
+      <c r="X5" s="138"/>
+      <c r="Y5" s="138"/>
+      <c r="Z5" s="141"/>
+      <c r="AA5" s="137">
         <f>AA6</f>
         <v>46294</v>
       </c>
-      <c r="AB5" s="133"/>
-      <c r="AC5" s="133"/>
-      <c r="AD5" s="133"/>
-      <c r="AE5" s="133"/>
-      <c r="AF5" s="133"/>
-      <c r="AG5" s="134"/>
-      <c r="AH5" s="135">
+      <c r="AB5" s="138"/>
+      <c r="AC5" s="138"/>
+      <c r="AD5" s="138"/>
+      <c r="AE5" s="138"/>
+      <c r="AF5" s="138"/>
+      <c r="AG5" s="139"/>
+      <c r="AH5" s="140">
         <f>AH6</f>
         <v>46301</v>
       </c>
-      <c r="AI5" s="133"/>
-      <c r="AJ5" s="133"/>
-      <c r="AK5" s="133"/>
-      <c r="AL5" s="133"/>
-      <c r="AM5" s="133"/>
-      <c r="AN5" s="136"/>
-      <c r="AO5" s="132">
+      <c r="AI5" s="138"/>
+      <c r="AJ5" s="138"/>
+      <c r="AK5" s="138"/>
+      <c r="AL5" s="138"/>
+      <c r="AM5" s="138"/>
+      <c r="AN5" s="141"/>
+      <c r="AO5" s="137">
         <f>AO6</f>
         <v>46308</v>
       </c>
-      <c r="AP5" s="133"/>
-      <c r="AQ5" s="133"/>
-      <c r="AR5" s="133"/>
-      <c r="AS5" s="133"/>
-      <c r="AT5" s="133"/>
-      <c r="AU5" s="134"/>
+      <c r="AP5" s="138"/>
+      <c r="AQ5" s="138"/>
+      <c r="AR5" s="138"/>
+      <c r="AS5" s="138"/>
+      <c r="AT5" s="138"/>
+      <c r="AU5" s="139"/>
       <c r="AV5" s="101" t="s">
         <v>24</v>
       </c>
@@ -2926,12 +3037,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" ht="21" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="F6" s="120">
+      <c r="F6" s="119">
         <f>F5</f>
         <v>46273</v>
       </c>
@@ -2943,7 +3054,7 @@
         <f t="shared" ref="H6:AN6" si="0">G6+1</f>
         <v>46275</v>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="121">
         <f t="shared" si="0"/>
         <v>46276</v>
       </c>
@@ -2955,11 +3066,11 @@
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
-      <c r="L6" s="124">
+      <c r="L6" s="123">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="M6" s="120">
+      <c r="M6" s="119">
         <f>L6+1</f>
         <v>46280</v>
       </c>
@@ -2967,11 +3078,11 @@
         <f>M6+1</f>
         <v>46281</v>
       </c>
-      <c r="O6" s="122">
+      <c r="O6" s="121">
         <f t="shared" si="0"/>
         <v>46282</v>
       </c>
-      <c r="P6" s="122">
+      <c r="P6" s="121">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
@@ -2995,11 +3106,11 @@
         <f>T6+1</f>
         <v>46288</v>
       </c>
-      <c r="V6" s="122">
+      <c r="V6" s="121">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-      <c r="W6" s="122">
+      <c r="W6" s="121">
         <f t="shared" si="0"/>
         <v>46290</v>
       </c>
@@ -3011,23 +3122,23 @@
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="Z6" s="126">
+      <c r="Z6" s="125">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="AA6" s="120">
+      <c r="AA6" s="119">
         <f>Z6+1</f>
         <v>46294</v>
       </c>
-      <c r="AB6" s="122">
+      <c r="AB6" s="121">
         <f>AA6+1</f>
         <v>46295</v>
       </c>
-      <c r="AC6" s="122">
+      <c r="AC6" s="121">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="AD6" s="122">
+      <c r="AD6" s="121">
         <f t="shared" si="0"/>
         <v>46297</v>
       </c>
@@ -3039,19 +3150,19 @@
         <f t="shared" si="0"/>
         <v>46299</v>
       </c>
-      <c r="AG6" s="124">
+      <c r="AG6" s="123">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="AH6" s="128">
+      <c r="AH6" s="127">
         <f>AG6+1</f>
         <v>46301</v>
       </c>
-      <c r="AI6" s="122">
+      <c r="AI6" s="121">
         <f>AH6+1</f>
         <v>46302</v>
       </c>
-      <c r="AJ6" s="122">
+      <c r="AJ6" s="121">
         <f t="shared" si="0"/>
         <v>46303</v>
       </c>
@@ -3071,19 +3182,19 @@
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="AO6" s="120">
+      <c r="AO6" s="119">
         <f>AN6+1</f>
         <v>46308</v>
       </c>
-      <c r="AP6" s="122">
+      <c r="AP6" s="121">
         <f>AO6+1</f>
         <v>46309</v>
       </c>
-      <c r="AQ6" s="122">
+      <c r="AQ6" s="121">
         <f t="shared" ref="AQ6" si="1">AP6+1</f>
         <v>46310</v>
       </c>
-      <c r="AR6" s="122">
+      <c r="AR6" s="121">
         <f t="shared" ref="AR6" si="2">AQ6+1</f>
         <v>46311</v>
       </c>
@@ -3114,7 +3225,9 @@
       <c r="AZ6" s="102">
         <v>46289</v>
       </c>
-      <c r="BA6" s="102"/>
+      <c r="BA6" s="102">
+        <v>46290</v>
+      </c>
       <c r="BB6" s="102"/>
       <c r="BC6" s="102"/>
       <c r="BD6" s="102"/>
@@ -3131,7 +3244,7 @@
       <c r="BO6" s="102"/>
       <c r="BP6" s="102"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:68" ht="30" customHeight="1" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3147,7 +3260,7 @@
       <c r="E7" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="121" t="str">
+      <c r="F7" s="120" t="str">
         <f t="shared" ref="F7:AK7" si="6">LEFT(TEXT(F6,"aaa"),1)</f>
         <v>火</v>
       </c>
@@ -3159,7 +3272,7 @@
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="I7" s="123" t="str">
+      <c r="I7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3171,11 +3284,11 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="L7" s="125" t="str">
+      <c r="L7" s="124" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="M7" s="121" t="str">
+      <c r="M7" s="120" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
@@ -3183,11 +3296,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="O7" s="123" t="str">
+      <c r="O7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="P7" s="123" t="str">
+      <c r="P7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3211,11 +3324,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="V7" s="123" t="str">
+      <c r="V7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="W7" s="123" t="str">
+      <c r="W7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3227,23 +3340,23 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="Z7" s="127" t="str">
+      <c r="Z7" s="126" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AA7" s="121" t="str">
+      <c r="AA7" s="120" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AB7" s="123" t="str">
+      <c r="AB7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AC7" s="123" t="str">
+      <c r="AC7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="AD7" s="123" t="str">
+      <c r="AD7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3255,19 +3368,19 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="AG7" s="125" t="str">
+      <c r="AG7" s="124" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AH7" s="129" t="str">
+      <c r="AH7" s="128" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AI7" s="123" t="str">
+      <c r="AI7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AJ7" s="123" t="str">
+      <c r="AJ7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
@@ -3287,19 +3400,19 @@
         <f t="shared" si="7"/>
         <v>月</v>
       </c>
-      <c r="AO7" s="121" t="str">
+      <c r="AO7" s="120" t="str">
         <f t="shared" si="7"/>
         <v>火</v>
       </c>
-      <c r="AP7" s="123" t="str">
+      <c r="AP7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>水</v>
       </c>
-      <c r="AQ7" s="123" t="str">
+      <c r="AQ7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>木</v>
       </c>
-      <c r="AR7" s="123" t="str">
+      <c r="AR7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>金</v>
       </c>
@@ -3379,7 +3492,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
@@ -3451,7 +3564,7 @@
       <c r="BO8" s="97"/>
       <c r="BP8" s="97"/>
     </row>
-    <row r="9" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -3525,7 +3638,7 @@
       <c r="BO9" s="98"/>
       <c r="BP9" s="98"/>
     </row>
-    <row r="10" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3547,8 +3660,8 @@
       <c r="I10" s="112"/>
       <c r="J10" s="71"/>
       <c r="K10" s="71"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="135"/>
       <c r="N10" s="71"/>
       <c r="O10" s="112"/>
       <c r="P10" s="71"/>
@@ -3598,7 +3711,9 @@
       <c r="AZ10" s="99">
         <v>1</v>
       </c>
-      <c r="BA10" s="99"/>
+      <c r="BA10" s="99">
+        <v>1</v>
+      </c>
       <c r="BB10" s="99"/>
       <c r="BC10" s="99"/>
       <c r="BD10" s="99"/>
@@ -3615,7 +3730,7 @@
       <c r="BO10" s="99"/>
       <c r="BP10" s="99"/>
     </row>
-    <row r="11" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3637,8 +3752,8 @@
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="135"/>
       <c r="N11" s="71"/>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
@@ -3688,7 +3803,9 @@
       <c r="AZ11" s="99">
         <v>1</v>
       </c>
-      <c r="BA11" s="99"/>
+      <c r="BA11" s="99">
+        <v>1</v>
+      </c>
       <c r="BB11" s="99"/>
       <c r="BC11" s="99"/>
       <c r="BD11" s="99"/>
@@ -3705,7 +3822,7 @@
       <c r="BO11" s="99"/>
       <c r="BP11" s="99"/>
     </row>
-    <row r="12" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="51" t="s">
         <v>18</v>
@@ -3724,23 +3841,23 @@
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
       <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="119"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="132"/>
       <c r="Q12" s="71"/>
       <c r="R12" s="71"/>
       <c r="S12" s="85"/>
       <c r="T12" s="77"/>
-      <c r="U12" s="71"/>
+      <c r="U12" s="86"/>
       <c r="V12" s="112"/>
-      <c r="W12" s="119"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="119"/>
-      <c r="AA12" s="70"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="77"/>
+      <c r="Y12" s="86"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="77"/>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
       <c r="AD12" s="71"/>
@@ -3774,7 +3891,9 @@
       <c r="AZ12" s="99">
         <v>0.15</v>
       </c>
-      <c r="BA12" s="98"/>
+      <c r="BA12" s="99">
+        <v>0.2</v>
+      </c>
       <c r="BB12" s="98"/>
       <c r="BC12" s="98"/>
       <c r="BD12" s="98"/>
@@ -3791,7 +3910,7 @@
       <c r="BO12" s="98"/>
       <c r="BP12" s="98"/>
     </row>
-    <row r="13" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="56"/>
       <c r="C13" s="57" t="s">
@@ -3863,7 +3982,7 @@
       <c r="BO13" s="98"/>
       <c r="BP13" s="98"/>
     </row>
-    <row r="14" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -3937,7 +4056,7 @@
       <c r="BO14" s="98"/>
       <c r="BP14" s="98"/>
     </row>
-    <row r="15" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="53" t="s">
         <v>20</v>
@@ -4021,7 +4140,7 @@
       <c r="BO15" s="98"/>
       <c r="BP15" s="98"/>
     </row>
-    <row r="16" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="66" t="s">
         <v>21</v>
@@ -4105,7 +4224,7 @@
       <c r="BO16" s="98"/>
       <c r="BP16" s="98"/>
     </row>
-    <row r="17" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="53" t="s">
         <v>22</v>
@@ -4189,7 +4308,7 @@
       <c r="BO17" s="98"/>
       <c r="BP17" s="98"/>
     </row>
-    <row r="18" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
       <c r="A18" s="8"/>
       <c r="B18" s="93"/>
       <c r="C18" s="94" t="s">
@@ -4261,23 +4380,23 @@
       <c r="BO18" s="100"/>
       <c r="BP18" s="100"/>
     </row>
-    <row r="20" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:68" ht="30" customHeight="1">
       <c r="B20" s="110"/>
       <c r="C20" s="12"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G21" s="130"/>
+    <row r="21" spans="1:68" ht="30" customHeight="1">
+      <c r="G21" s="129"/>
       <c r="H21" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:68" ht="30" customHeight="1">
       <c r="E22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:68" ht="30" customHeight="1">
       <c r="E23" s="106" t="s">
         <v>29</v>
       </c>
@@ -4324,7 +4443,7 @@
       <c r="AT23" s="109"/>
       <c r="AU23" s="104"/>
     </row>
-    <row r="24" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:68" ht="30" customHeight="1">
       <c r="E24" s="107" t="s">
         <v>30</v>
       </c>
@@ -4335,14 +4454,14 @@
       <c r="J24" s="105"/>
       <c r="K24" s="105"/>
       <c r="L24" s="104"/>
-      <c r="M24" s="131" t="s">
+      <c r="M24" s="130" t="s">
         <v>38</v>
       </c>
       <c r="N24" s="105"/>
-      <c r="O24" s="131" t="s">
+      <c r="O24" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="P24" s="131" t="s">
+      <c r="P24" s="130" t="s">
         <v>38</v>
       </c>
       <c r="Q24" s="105"/>
@@ -4377,7 +4496,7 @@
       <c r="AT24" s="105"/>
       <c r="AU24" s="104"/>
     </row>
-    <row r="25" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:68" ht="30" customHeight="1">
       <c r="E25" s="106" t="s">
         <v>31</v>
       </c>
@@ -4390,10 +4509,10 @@
       <c r="L25" s="104"/>
       <c r="M25" s="104"/>
       <c r="N25" s="105"/>
-      <c r="O25" s="131" t="s">
+      <c r="O25" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="P25" s="131" t="s">
+      <c r="P25" s="130" t="s">
         <v>38</v>
       </c>
       <c r="Q25" s="105"/>
@@ -4456,7 +4575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:68" ht="30" customHeight="1">
       <c r="E26" s="107" t="s">
         <v>32</v>
       </c>
@@ -4503,7 +4622,7 @@
       <c r="AT26" s="105"/>
       <c r="AU26" s="104"/>
     </row>
-    <row r="27" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:68" ht="30" customHeight="1">
       <c r="E27" s="106" t="s">
         <v>33</v>
       </c>
@@ -4523,7 +4642,7 @@
       <c r="S27" s="105"/>
       <c r="T27" s="105"/>
       <c r="U27" s="105"/>
-      <c r="V27" s="131" t="s">
+      <c r="V27" s="130" t="s">
         <v>38</v>
       </c>
       <c r="W27" s="104"/>
@@ -4531,7 +4650,7 @@
       <c r="Y27" s="105"/>
       <c r="Z27" s="104"/>
       <c r="AA27" s="104"/>
-      <c r="AB27" s="131" t="s">
+      <c r="AB27" s="130" t="s">
         <v>38</v>
       </c>
       <c r="AC27" s="104"/>
@@ -4554,7 +4673,7 @@
       <c r="AT27" s="105"/>
       <c r="AU27" s="104"/>
     </row>
-    <row r="28" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:68" ht="30" customHeight="1">
       <c r="E28" s="107" t="s">
         <v>34</v>
       </c>
@@ -4575,7 +4694,7 @@
       <c r="T28" s="105"/>
       <c r="U28" s="105"/>
       <c r="V28" s="104"/>
-      <c r="W28" s="131" t="s">
+      <c r="W28" s="130" t="s">
         <v>38</v>
       </c>
       <c r="X28" s="105"/>
@@ -4679,6 +4798,7 @@
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4769,7 +4889,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781B8887-CE6A-4A0E-8262-8920C09EEF86}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData/>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4779,117 +4899,117 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE6A2FC-300A-4B2A-BCE2-26C39F90CFA2}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="82">
         <v>46023</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="82">
         <v>46034</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="82">
         <v>46064</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="82">
         <v>46076</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="82">
         <v>46101</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="82">
         <v>46141</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="82">
         <v>46145</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="82">
         <v>46146</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="82">
         <v>46147</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="82">
         <v>46223</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="82">
         <v>46245</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" s="82">
         <v>46274</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" s="82">
         <v>46275</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="82">
         <v>46281</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="82">
         <v>46286</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="82">
         <v>46287</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" s="82">
         <v>46288</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="82">
         <v>46304</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="82">
         <v>46307</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="82">
         <v>46329</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="82">
         <v>46349</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="82">
         <v>46379</v>
       </c>

--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DD7611-B2B2-4DB1-BEDC-3FF3BB456B33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255165D8-9138-4408-A3F9-4A8C3337887F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13755" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="41">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -311,6 +311,13 @@
     </rPh>
     <rPh sb="7" eb="9">
       <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>全員</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -866,7 +873,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -1639,6 +1646,51 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC0C0C0"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1714,7 +1766,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2032,9 +2084,6 @@
     <xf numFmtId="0" fontId="31" fillId="38" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="180" fontId="29" fillId="49" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2067,6 +2116,21 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="50" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="24" fillId="50" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2451,13 +2515,13 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFC0C0C0"/>
+      <color rgb="FF969696"/>
       <color rgb="FFFFFF66"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FF215881"/>
       <color rgb="FF42648A"/>
-      <color rgb="FF969696"/>
-      <color rgb="FFC0C0C0"/>
       <color rgb="FF427FC2"/>
       <color rgb="FF44678E"/>
       <color rgb="FF4A6F9C"/>
@@ -2774,7 +2838,7 @@
       <c r="J2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M2" s="119"/>
+      <c r="M2" s="132"/>
       <c r="N2" s="6" t="s">
         <v>37</v>
       </c>
@@ -2789,8 +2853,8 @@
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
     </row>
     <row r="5" spans="1:68" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2802,66 +2866,66 @@
       <c r="C5" s="15"/>
       <c r="D5" s="55"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="132">
+      <c r="F5" s="136">
         <f>D10</f>
         <v>46273</v>
       </c>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="132">
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="138"/>
+      <c r="M5" s="136">
         <f>M6</f>
         <v>46280</v>
       </c>
-      <c r="N5" s="133"/>
-      <c r="O5" s="133"/>
-      <c r="P5" s="133"/>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="135">
+      <c r="N5" s="137"/>
+      <c r="O5" s="137"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="137"/>
+      <c r="R5" s="137"/>
+      <c r="S5" s="138"/>
+      <c r="T5" s="139">
         <f>T6</f>
         <v>46287</v>
       </c>
-      <c r="U5" s="133"/>
-      <c r="V5" s="133"/>
-      <c r="W5" s="133"/>
-      <c r="X5" s="133"/>
-      <c r="Y5" s="133"/>
-      <c r="Z5" s="136"/>
-      <c r="AA5" s="132">
+      <c r="U5" s="137"/>
+      <c r="V5" s="137"/>
+      <c r="W5" s="137"/>
+      <c r="X5" s="137"/>
+      <c r="Y5" s="137"/>
+      <c r="Z5" s="140"/>
+      <c r="AA5" s="136">
         <f>AA6</f>
         <v>46294</v>
       </c>
-      <c r="AB5" s="133"/>
-      <c r="AC5" s="133"/>
-      <c r="AD5" s="133"/>
-      <c r="AE5" s="133"/>
-      <c r="AF5" s="133"/>
-      <c r="AG5" s="134"/>
-      <c r="AH5" s="135">
+      <c r="AB5" s="137"/>
+      <c r="AC5" s="137"/>
+      <c r="AD5" s="137"/>
+      <c r="AE5" s="137"/>
+      <c r="AF5" s="137"/>
+      <c r="AG5" s="138"/>
+      <c r="AH5" s="139">
         <f>AH6</f>
         <v>46301</v>
       </c>
-      <c r="AI5" s="133"/>
-      <c r="AJ5" s="133"/>
-      <c r="AK5" s="133"/>
-      <c r="AL5" s="133"/>
-      <c r="AM5" s="133"/>
-      <c r="AN5" s="136"/>
-      <c r="AO5" s="132">
+      <c r="AI5" s="137"/>
+      <c r="AJ5" s="137"/>
+      <c r="AK5" s="137"/>
+      <c r="AL5" s="137"/>
+      <c r="AM5" s="137"/>
+      <c r="AN5" s="140"/>
+      <c r="AO5" s="136">
         <f>AO6</f>
         <v>46308</v>
       </c>
-      <c r="AP5" s="133"/>
-      <c r="AQ5" s="133"/>
-      <c r="AR5" s="133"/>
-      <c r="AS5" s="133"/>
-      <c r="AT5" s="133"/>
-      <c r="AU5" s="134"/>
+      <c r="AP5" s="137"/>
+      <c r="AQ5" s="137"/>
+      <c r="AR5" s="137"/>
+      <c r="AS5" s="137"/>
+      <c r="AT5" s="137"/>
+      <c r="AU5" s="138"/>
       <c r="AV5" s="101" t="s">
         <v>24</v>
       </c>
@@ -2931,7 +2995,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="F6" s="120">
+      <c r="F6" s="119">
         <f>F5</f>
         <v>46273</v>
       </c>
@@ -2943,7 +3007,7 @@
         <f t="shared" ref="H6:AN6" si="0">G6+1</f>
         <v>46275</v>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="121">
         <f t="shared" si="0"/>
         <v>46276</v>
       </c>
@@ -2955,11 +3019,11 @@
         <f t="shared" si="0"/>
         <v>46278</v>
       </c>
-      <c r="L6" s="124">
+      <c r="L6" s="123">
         <f t="shared" si="0"/>
         <v>46279</v>
       </c>
-      <c r="M6" s="120">
+      <c r="M6" s="119">
         <f>L6+1</f>
         <v>46280</v>
       </c>
@@ -2967,11 +3031,11 @@
         <f>M6+1</f>
         <v>46281</v>
       </c>
-      <c r="O6" s="122">
+      <c r="O6" s="121">
         <f t="shared" si="0"/>
         <v>46282</v>
       </c>
-      <c r="P6" s="122">
+      <c r="P6" s="121">
         <f t="shared" si="0"/>
         <v>46283</v>
       </c>
@@ -2995,11 +3059,11 @@
         <f>T6+1</f>
         <v>46288</v>
       </c>
-      <c r="V6" s="122">
+      <c r="V6" s="121">
         <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-      <c r="W6" s="122">
+      <c r="W6" s="121">
         <f t="shared" si="0"/>
         <v>46290</v>
       </c>
@@ -3011,23 +3075,23 @@
         <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="Z6" s="126">
+      <c r="Z6" s="125">
         <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="AA6" s="120">
+      <c r="AA6" s="119">
         <f>Z6+1</f>
         <v>46294</v>
       </c>
-      <c r="AB6" s="122">
+      <c r="AB6" s="121">
         <f>AA6+1</f>
         <v>46295</v>
       </c>
-      <c r="AC6" s="122">
+      <c r="AC6" s="121">
         <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="AD6" s="122">
+      <c r="AD6" s="121">
         <f t="shared" si="0"/>
         <v>46297</v>
       </c>
@@ -3039,19 +3103,19 @@
         <f t="shared" si="0"/>
         <v>46299</v>
       </c>
-      <c r="AG6" s="124">
+      <c r="AG6" s="123">
         <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="AH6" s="128">
+      <c r="AH6" s="127">
         <f>AG6+1</f>
         <v>46301</v>
       </c>
-      <c r="AI6" s="122">
+      <c r="AI6" s="121">
         <f>AH6+1</f>
         <v>46302</v>
       </c>
-      <c r="AJ6" s="122">
+      <c r="AJ6" s="121">
         <f t="shared" si="0"/>
         <v>46303</v>
       </c>
@@ -3071,19 +3135,19 @@
         <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="AO6" s="120">
+      <c r="AO6" s="119">
         <f>AN6+1</f>
         <v>46308</v>
       </c>
-      <c r="AP6" s="122">
+      <c r="AP6" s="121">
         <f>AO6+1</f>
         <v>46309</v>
       </c>
-      <c r="AQ6" s="122">
+      <c r="AQ6" s="121">
         <f t="shared" ref="AQ6" si="1">AP6+1</f>
         <v>46310</v>
       </c>
-      <c r="AR6" s="122">
+      <c r="AR6" s="121">
         <f t="shared" ref="AR6" si="2">AQ6+1</f>
         <v>46311</v>
       </c>
@@ -3114,8 +3178,12 @@
       <c r="AZ6" s="102">
         <v>46289</v>
       </c>
-      <c r="BA6" s="102"/>
-      <c r="BB6" s="102"/>
+      <c r="BA6" s="102">
+        <v>46290</v>
+      </c>
+      <c r="BB6" s="102">
+        <v>46293</v>
+      </c>
       <c r="BC6" s="102"/>
       <c r="BD6" s="102"/>
       <c r="BE6" s="102"/>
@@ -3147,7 +3215,7 @@
       <c r="E7" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="121" t="str">
+      <c r="F7" s="120" t="str">
         <f t="shared" ref="F7:AK7" si="6">LEFT(TEXT(F6,"aaa"),1)</f>
         <v>火</v>
       </c>
@@ -3159,7 +3227,7 @@
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="I7" s="123" t="str">
+      <c r="I7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3171,11 +3239,11 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="L7" s="125" t="str">
+      <c r="L7" s="124" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="M7" s="121" t="str">
+      <c r="M7" s="120" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
@@ -3183,11 +3251,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="O7" s="123" t="str">
+      <c r="O7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="P7" s="123" t="str">
+      <c r="P7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3211,11 +3279,11 @@
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="V7" s="123" t="str">
+      <c r="V7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="W7" s="123" t="str">
+      <c r="W7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3227,23 +3295,23 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="Z7" s="127" t="str">
+      <c r="Z7" s="126" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AA7" s="121" t="str">
+      <c r="AA7" s="120" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AB7" s="123" t="str">
+      <c r="AB7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AC7" s="123" t="str">
+      <c r="AC7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
-      <c r="AD7" s="123" t="str">
+      <c r="AD7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>金</v>
       </c>
@@ -3255,19 +3323,19 @@
         <f t="shared" si="6"/>
         <v>日</v>
       </c>
-      <c r="AG7" s="125" t="str">
+      <c r="AG7" s="124" t="str">
         <f t="shared" si="6"/>
         <v>月</v>
       </c>
-      <c r="AH7" s="129" t="str">
+      <c r="AH7" s="128" t="str">
         <f t="shared" si="6"/>
         <v>火</v>
       </c>
-      <c r="AI7" s="123" t="str">
+      <c r="AI7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>水</v>
       </c>
-      <c r="AJ7" s="123" t="str">
+      <c r="AJ7" s="122" t="str">
         <f t="shared" si="6"/>
         <v>木</v>
       </c>
@@ -3287,19 +3355,19 @@
         <f t="shared" si="7"/>
         <v>月</v>
       </c>
-      <c r="AO7" s="121" t="str">
+      <c r="AO7" s="120" t="str">
         <f t="shared" si="7"/>
         <v>火</v>
       </c>
-      <c r="AP7" s="123" t="str">
+      <c r="AP7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>水</v>
       </c>
-      <c r="AQ7" s="123" t="str">
+      <c r="AQ7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>木</v>
       </c>
-      <c r="AR7" s="123" t="str">
+      <c r="AR7" s="122" t="str">
         <f t="shared" si="7"/>
         <v>金</v>
       </c>
@@ -3533,7 +3601,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D10" s="42">
         <v>46273</v>
@@ -3547,8 +3615,8 @@
       <c r="I10" s="112"/>
       <c r="J10" s="71"/>
       <c r="K10" s="71"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="134"/>
       <c r="N10" s="71"/>
       <c r="O10" s="112"/>
       <c r="P10" s="71"/>
@@ -3598,8 +3666,12 @@
       <c r="AZ10" s="99">
         <v>1</v>
       </c>
-      <c r="BA10" s="99"/>
-      <c r="BB10" s="99"/>
+      <c r="BA10" s="99">
+        <v>1</v>
+      </c>
+      <c r="BB10" s="99">
+        <v>1</v>
+      </c>
       <c r="BC10" s="99"/>
       <c r="BD10" s="99"/>
       <c r="BE10" s="99"/>
@@ -3623,7 +3695,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D11" s="58">
         <v>46280</v>
@@ -3637,8 +3709,8 @@
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
-      <c r="L11" s="112"/>
-      <c r="M11" s="112"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="134"/>
       <c r="N11" s="71"/>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
@@ -3688,8 +3760,12 @@
       <c r="AZ11" s="99">
         <v>1</v>
       </c>
-      <c r="BA11" s="99"/>
-      <c r="BB11" s="99"/>
+      <c r="BA11" s="99">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="99">
+        <v>1</v>
+      </c>
       <c r="BC11" s="99"/>
       <c r="BD11" s="99"/>
       <c r="BE11" s="99"/>
@@ -3711,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D12" s="42">
         <v>46283</v>
@@ -3724,23 +3800,23 @@
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
       <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="119"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="135"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="132"/>
       <c r="Q12" s="71"/>
       <c r="R12" s="71"/>
       <c r="S12" s="85"/>
       <c r="T12" s="77"/>
-      <c r="U12" s="71"/>
+      <c r="U12" s="86"/>
       <c r="V12" s="112"/>
-      <c r="W12" s="119"/>
-      <c r="X12" s="71"/>
-      <c r="Y12" s="71"/>
-      <c r="Z12" s="119"/>
-      <c r="AA12" s="70"/>
+      <c r="W12" s="112"/>
+      <c r="X12" s="77"/>
+      <c r="Y12" s="86"/>
+      <c r="Z12" s="112"/>
+      <c r="AA12" s="77"/>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
       <c r="AD12" s="71"/>
@@ -3774,8 +3850,12 @@
       <c r="AZ12" s="99">
         <v>0.15</v>
       </c>
-      <c r="BA12" s="98"/>
-      <c r="BB12" s="98"/>
+      <c r="BA12" s="99">
+        <v>0.2</v>
+      </c>
+      <c r="BB12" s="99">
+        <v>0.6</v>
+      </c>
       <c r="BC12" s="98"/>
       <c r="BD12" s="98"/>
       <c r="BE12" s="98"/>
@@ -4267,7 +4347,7 @@
       <c r="E20" s="13"/>
     </row>
     <row r="21" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G21" s="130"/>
+      <c r="G21" s="129"/>
       <c r="H21" s="6" t="s">
         <v>39</v>
       </c>
@@ -4335,14 +4415,14 @@
       <c r="J24" s="105"/>
       <c r="K24" s="105"/>
       <c r="L24" s="104"/>
-      <c r="M24" s="131" t="s">
+      <c r="M24" s="130" t="s">
         <v>38</v>
       </c>
       <c r="N24" s="105"/>
-      <c r="O24" s="131" t="s">
+      <c r="O24" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="P24" s="131" t="s">
+      <c r="P24" s="130" t="s">
         <v>38</v>
       </c>
       <c r="Q24" s="105"/>
@@ -4390,10 +4470,10 @@
       <c r="L25" s="104"/>
       <c r="M25" s="104"/>
       <c r="N25" s="105"/>
-      <c r="O25" s="131" t="s">
+      <c r="O25" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="P25" s="131" t="s">
+      <c r="P25" s="130" t="s">
         <v>38</v>
       </c>
       <c r="Q25" s="105"/>
@@ -4523,7 +4603,7 @@
       <c r="S27" s="105"/>
       <c r="T27" s="105"/>
       <c r="U27" s="105"/>
-      <c r="V27" s="131" t="s">
+      <c r="V27" s="130" t="s">
         <v>38</v>
       </c>
       <c r="W27" s="104"/>
@@ -4531,7 +4611,7 @@
       <c r="Y27" s="105"/>
       <c r="Z27" s="104"/>
       <c r="AA27" s="104"/>
-      <c r="AB27" s="131" t="s">
+      <c r="AB27" s="130" t="s">
         <v>38</v>
       </c>
       <c r="AC27" s="104"/>
@@ -4575,7 +4655,7 @@
       <c r="T28" s="105"/>
       <c r="U28" s="105"/>
       <c r="V28" s="104"/>
-      <c r="W28" s="131" t="s">
+      <c r="W28" s="130" t="s">
         <v>38</v>
       </c>
       <c r="X28" s="105"/>
@@ -4902,12 +4982,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5199,29 +5290,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5248,20 +5339,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F94A5E-39BB-4F1F-980B-C26BBB28B76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F902F6-8D29-4437-BB2C-4CB1CA66EB85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15390" windowHeight="11895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -30,44 +30,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>作成者</author>
-  </authors>
-  <commentList>
-    <comment ref="Z12" authorId="0" shapeId="0" xr:uid="{ED8264A6-3574-4C67-9311-B0156B135D83}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>作成者:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-実装の予定をたてる</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="42">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -350,6 +314,20 @@
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
+  <si>
+    <t>全員</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>欠席</t>
+    <rPh sb="0" eb="2">
+      <t>ケッセキ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
 </sst>
 </file>
 
@@ -365,7 +343,7 @@
     <numFmt numFmtId="180" formatCode="d"/>
     <numFmt numFmtId="181" formatCode="yy/mm/dd;@"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,21 +587,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Meiryo UI"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -1810,7 +1773,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2166,16 +2129,22 @@
     <xf numFmtId="0" fontId="24" fillId="48" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="45" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="48" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="45" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2562,9 +2531,9 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFFFFF66"/>
       <color rgb="FFC0C0C0"/>
       <color rgb="FF969696"/>
-      <color rgb="FFFFFF66"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFFFFFCC"/>
       <color rgb="FF215881"/>
@@ -2847,12 +2816,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BP28"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="8" customWidth="1"/>
     <col min="2" max="2" width="20.21875" style="6" customWidth="1"/>
@@ -2865,7 +2834,7 @@
     <col min="69" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="21.6" customHeight="1">
+    <row r="1" spans="1:68" ht="21.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -2873,7 +2842,7 @@
       <c r="E1" s="5"/>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:68" ht="30" customHeight="1">
+    <row r="2" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
@@ -2890,20 +2859,20 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:68" ht="10.9" customHeight="1">
+    <row r="3" spans="1:68" ht="10.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="2"/>
       <c r="F3" s="10"/>
     </row>
-    <row r="4" spans="1:68" ht="22.9" customHeight="1">
+    <row r="4" spans="1:68" ht="22.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="142"/>
-      <c r="E4" s="142"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="144"/>
     </row>
-    <row r="5" spans="1:68" ht="25.9" customHeight="1">
+    <row r="5" spans="1:68" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -2913,66 +2882,66 @@
       <c r="C5" s="15"/>
       <c r="D5" s="55"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="137">
+      <c r="F5" s="139">
         <f>D10</f>
         <v>46273</v>
       </c>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="138"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="138"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="137">
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="139">
         <f>M6</f>
         <v>46280</v>
       </c>
-      <c r="N5" s="138"/>
-      <c r="O5" s="138"/>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="138"/>
-      <c r="R5" s="138"/>
-      <c r="S5" s="139"/>
-      <c r="T5" s="140">
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="141"/>
+      <c r="T5" s="142">
         <f>T6</f>
         <v>46287</v>
       </c>
-      <c r="U5" s="138"/>
-      <c r="V5" s="138"/>
-      <c r="W5" s="138"/>
-      <c r="X5" s="138"/>
-      <c r="Y5" s="138"/>
-      <c r="Z5" s="141"/>
-      <c r="AA5" s="137">
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
+      <c r="W5" s="140"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="140"/>
+      <c r="Z5" s="143"/>
+      <c r="AA5" s="139">
         <f>AA6</f>
         <v>46294</v>
       </c>
-      <c r="AB5" s="138"/>
-      <c r="AC5" s="138"/>
-      <c r="AD5" s="138"/>
-      <c r="AE5" s="138"/>
-      <c r="AF5" s="138"/>
-      <c r="AG5" s="139"/>
-      <c r="AH5" s="140">
+      <c r="AB5" s="140"/>
+      <c r="AC5" s="140"/>
+      <c r="AD5" s="140"/>
+      <c r="AE5" s="140"/>
+      <c r="AF5" s="140"/>
+      <c r="AG5" s="141"/>
+      <c r="AH5" s="142">
         <f>AH6</f>
         <v>46301</v>
       </c>
-      <c r="AI5" s="138"/>
-      <c r="AJ5" s="138"/>
-      <c r="AK5" s="138"/>
-      <c r="AL5" s="138"/>
-      <c r="AM5" s="138"/>
-      <c r="AN5" s="141"/>
-      <c r="AO5" s="137">
+      <c r="AI5" s="140"/>
+      <c r="AJ5" s="140"/>
+      <c r="AK5" s="140"/>
+      <c r="AL5" s="140"/>
+      <c r="AM5" s="140"/>
+      <c r="AN5" s="143"/>
+      <c r="AO5" s="139">
         <f>AO6</f>
         <v>46308</v>
       </c>
-      <c r="AP5" s="138"/>
-      <c r="AQ5" s="138"/>
-      <c r="AR5" s="138"/>
-      <c r="AS5" s="138"/>
-      <c r="AT5" s="138"/>
-      <c r="AU5" s="139"/>
+      <c r="AP5" s="140"/>
+      <c r="AQ5" s="140"/>
+      <c r="AR5" s="140"/>
+      <c r="AS5" s="140"/>
+      <c r="AT5" s="140"/>
+      <c r="AU5" s="141"/>
       <c r="AV5" s="101" t="s">
         <v>24</v>
       </c>
@@ -3037,7 +3006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="21" customHeight="1">
+    <row r="6" spans="1:68" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -3228,7 +3197,9 @@
       <c r="BA6" s="102">
         <v>46290</v>
       </c>
-      <c r="BB6" s="102"/>
+      <c r="BB6" s="102">
+        <v>46293</v>
+      </c>
       <c r="BC6" s="102"/>
       <c r="BD6" s="102"/>
       <c r="BE6" s="102"/>
@@ -3244,7 +3215,7 @@
       <c r="BO6" s="102"/>
       <c r="BP6" s="102"/>
     </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" thickBot="1">
+    <row r="7" spans="1:68" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3492,7 +3463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1">
+    <row r="8" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
@@ -3564,7 +3535,7 @@
       <c r="BO8" s="97"/>
       <c r="BP8" s="97"/>
     </row>
-    <row r="9" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="9" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
@@ -3638,7 +3609,7 @@
       <c r="BO9" s="98"/>
       <c r="BP9" s="98"/>
     </row>
-    <row r="10" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="10" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3646,7 +3617,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D10" s="42">
         <v>46273</v>
@@ -3660,8 +3631,8 @@
       <c r="I10" s="112"/>
       <c r="J10" s="71"/>
       <c r="K10" s="71"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="135"/>
+      <c r="L10" s="133"/>
+      <c r="M10" s="134"/>
       <c r="N10" s="71"/>
       <c r="O10" s="112"/>
       <c r="P10" s="71"/>
@@ -3714,8 +3685,12 @@
       <c r="BA10" s="99">
         <v>1</v>
       </c>
-      <c r="BB10" s="99"/>
-      <c r="BC10" s="99"/>
+      <c r="BB10" s="99">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="99">
+        <v>1</v>
+      </c>
       <c r="BD10" s="99"/>
       <c r="BE10" s="99"/>
       <c r="BF10" s="99"/>
@@ -3730,7 +3705,7 @@
       <c r="BO10" s="99"/>
       <c r="BP10" s="99"/>
     </row>
-    <row r="11" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="11" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3738,7 +3713,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D11" s="58">
         <v>46280</v>
@@ -3752,8 +3727,8 @@
       <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="135"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="134"/>
       <c r="N11" s="71"/>
       <c r="O11" s="112"/>
       <c r="P11" s="112"/>
@@ -3806,8 +3781,12 @@
       <c r="BA11" s="99">
         <v>1</v>
       </c>
-      <c r="BB11" s="99"/>
-      <c r="BC11" s="99"/>
+      <c r="BB11" s="99">
+        <v>1</v>
+      </c>
+      <c r="BC11" s="99">
+        <v>1</v>
+      </c>
       <c r="BD11" s="99"/>
       <c r="BE11" s="99"/>
       <c r="BF11" s="99"/>
@@ -3822,13 +3801,13 @@
       <c r="BO11" s="99"/>
       <c r="BP11" s="99"/>
     </row>
-    <row r="12" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="12" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="51" t="s">
         <v>18</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D12" s="42">
         <v>46283</v>
@@ -3842,7 +3821,7 @@
       <c r="I12" s="71"/>
       <c r="J12" s="71"/>
       <c r="K12" s="86"/>
-      <c r="L12" s="136"/>
+      <c r="L12" s="135"/>
       <c r="M12" s="70"/>
       <c r="N12" s="86"/>
       <c r="O12" s="131"/>
@@ -3856,7 +3835,7 @@
       <c r="W12" s="112"/>
       <c r="X12" s="77"/>
       <c r="Y12" s="86"/>
-      <c r="Z12" s="133"/>
+      <c r="Z12" s="112"/>
       <c r="AA12" s="77"/>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
@@ -3894,8 +3873,12 @@
       <c r="BA12" s="99">
         <v>0.2</v>
       </c>
-      <c r="BB12" s="98"/>
-      <c r="BC12" s="98"/>
+      <c r="BB12" s="99">
+        <v>0.6</v>
+      </c>
+      <c r="BC12" s="99">
+        <v>0.8</v>
+      </c>
       <c r="BD12" s="98"/>
       <c r="BE12" s="98"/>
       <c r="BF12" s="98"/>
@@ -3910,7 +3893,7 @@
       <c r="BO12" s="98"/>
       <c r="BP12" s="98"/>
     </row>
-    <row r="13" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" thickBot="1">
+    <row r="13" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="56"/>
       <c r="C13" s="57" t="s">
@@ -3982,7 +3965,7 @@
       <c r="BO13" s="98"/>
       <c r="BP13" s="98"/>
     </row>
-    <row r="14" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="14" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -4056,7 +4039,7 @@
       <c r="BO14" s="98"/>
       <c r="BP14" s="98"/>
     </row>
-    <row r="15" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="15" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="53" t="s">
         <v>20</v>
@@ -4091,15 +4074,15 @@
       <c r="X15" s="71"/>
       <c r="Y15" s="71"/>
       <c r="Z15" s="86"/>
-      <c r="AA15" s="70"/>
-      <c r="AB15" s="71"/>
-      <c r="AC15" s="71"/>
-      <c r="AD15" s="71"/>
+      <c r="AA15" s="134"/>
+      <c r="AB15" s="136"/>
+      <c r="AC15" s="136"/>
+      <c r="AD15" s="136"/>
       <c r="AE15" s="71"/>
       <c r="AF15" s="71"/>
-      <c r="AG15" s="85"/>
-      <c r="AH15" s="77"/>
-      <c r="AI15" s="71"/>
+      <c r="AG15" s="137"/>
+      <c r="AH15" s="138"/>
+      <c r="AI15" s="136"/>
       <c r="AJ15" s="71"/>
       <c r="AK15" s="71"/>
       <c r="AL15" s="71"/>
@@ -4125,7 +4108,9 @@
       <c r="AZ15" s="98"/>
       <c r="BA15" s="98"/>
       <c r="BB15" s="98"/>
-      <c r="BC15" s="98"/>
+      <c r="BC15" s="99">
+        <v>0.15</v>
+      </c>
       <c r="BD15" s="98"/>
       <c r="BE15" s="98"/>
       <c r="BF15" s="98"/>
@@ -4140,7 +4125,7 @@
       <c r="BO15" s="98"/>
       <c r="BP15" s="98"/>
     </row>
-    <row r="16" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="16" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8"/>
       <c r="B16" s="66" t="s">
         <v>21</v>
@@ -4224,7 +4209,7 @@
       <c r="BO16" s="98"/>
       <c r="BP16" s="98"/>
     </row>
-    <row r="17" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="17" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
       <c r="B17" s="53" t="s">
         <v>22</v>
@@ -4308,7 +4293,7 @@
       <c r="BO17" s="98"/>
       <c r="BP17" s="98"/>
     </row>
-    <row r="18" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="18" spans="1:68" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="93"/>
       <c r="C18" s="94" t="s">
@@ -4380,23 +4365,23 @@
       <c r="BO18" s="100"/>
       <c r="BP18" s="100"/>
     </row>
-    <row r="20" spans="1:68" ht="30" customHeight="1">
+    <row r="20" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="110"/>
       <c r="C20" s="12"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:68" ht="30" customHeight="1">
+    <row r="21" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G21" s="129"/>
       <c r="H21" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="30" customHeight="1">
+    <row r="22" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="30" customHeight="1">
+    <row r="23" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E23" s="106" t="s">
         <v>29</v>
       </c>
@@ -4443,7 +4428,7 @@
       <c r="AT23" s="109"/>
       <c r="AU23" s="104"/>
     </row>
-    <row r="24" spans="1:68" ht="30" customHeight="1">
+    <row r="24" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E24" s="107" t="s">
         <v>30</v>
       </c>
@@ -4496,7 +4481,7 @@
       <c r="AT24" s="105"/>
       <c r="AU24" s="104"/>
     </row>
-    <row r="25" spans="1:68" ht="30" customHeight="1">
+    <row r="25" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E25" s="106" t="s">
         <v>31</v>
       </c>
@@ -4575,7 +4560,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:68" ht="30" customHeight="1">
+    <row r="26" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E26" s="107" t="s">
         <v>32</v>
       </c>
@@ -4622,7 +4607,7 @@
       <c r="AT26" s="105"/>
       <c r="AU26" s="104"/>
     </row>
-    <row r="27" spans="1:68" ht="30" customHeight="1">
+    <row r="27" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E27" s="106" t="s">
         <v>33</v>
       </c>
@@ -4673,7 +4658,7 @@
       <c r="AT27" s="105"/>
       <c r="AU27" s="104"/>
     </row>
-    <row r="28" spans="1:68" ht="30" customHeight="1">
+    <row r="28" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E28" s="107" t="s">
         <v>34</v>
       </c>
@@ -4700,7 +4685,9 @@
       <c r="X28" s="105"/>
       <c r="Y28" s="105"/>
       <c r="Z28" s="104"/>
-      <c r="AA28" s="104"/>
+      <c r="AA28" s="130" t="s">
+        <v>41</v>
+      </c>
       <c r="AB28" s="104"/>
       <c r="AC28" s="104"/>
       <c r="AD28" s="104"/>
@@ -4798,7 +4785,6 @@
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4889,7 +4875,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{781B8887-CE6A-4A0E-8262-8920C09EEF86}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4899,117 +4885,117 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BE6A2FC-300A-4B2A-BCE2-26C39F90CFA2}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="82">
         <v>46023</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="82">
         <v>46034</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="82">
         <v>46064</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="82">
         <v>46076</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="82">
         <v>46101</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="82">
         <v>46141</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="82">
         <v>46145</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="82">
         <v>46146</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="82">
         <v>46147</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="82">
         <v>46223</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="82">
         <v>46245</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="82">
         <v>46274</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="82">
         <v>46275</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="82">
         <v>46281</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="82">
         <v>46286</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="82">
         <v>46287</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="82">
         <v>46288</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="82">
         <v>46304</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="82">
         <v>46307</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="82">
         <v>46329</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="82">
         <v>46349</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="82">
         <v>46379</v>
       </c>
@@ -5022,15 +5008,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5318,7 +5295,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -5338,15 +5315,16 @@
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5367,21 +5345,29 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9762C880-45E8-49DD-AAB6-3A5ED6098C9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E53FBF-3197-4805-B086-48000F6CF142}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13755" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="42">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -328,19 +328,6 @@
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
-  <si>
-    <t>発表予定日</t>
-  </si>
-  <si>
-    <t>中間発表</t>
-    <rPh sb="0" eb="2">
-      <t>チュウカン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッピョウ</t>
-    </rPh>
-    <phoneticPr fontId="19"/>
-  </si>
 </sst>
 </file>
 
@@ -604,7 +591,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="52">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -892,12 +879,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="62">
     <border>
@@ -1792,7 +1773,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2184,7 +2165,6 @@
     <xf numFmtId="179" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="54">
     <cellStyle name="20% - アクセント 1" xfId="31" builtinId="30" customBuiltin="1"/>
@@ -2878,10 +2858,6 @@
       <c r="N2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="6" t="s">
-        <v>42</v>
-      </c>
     </row>
     <row r="3" spans="1:68" ht="10.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="2"/>
@@ -3225,12 +3201,14 @@
         <v>46293</v>
       </c>
       <c r="BC6" s="102">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="BD6" s="102">
-        <v>46295</v>
-      </c>
-      <c r="BE6" s="102"/>
+        <v>46296</v>
+      </c>
+      <c r="BE6" s="102">
+        <v>46267</v>
+      </c>
       <c r="BF6" s="102"/>
       <c r="BG6" s="102"/>
       <c r="BH6" s="102"/>
@@ -3720,9 +3698,11 @@
         <v>1</v>
       </c>
       <c r="BD10" s="99">
-        <v>0.95</v>
-      </c>
-      <c r="BE10" s="99"/>
+        <v>1</v>
+      </c>
+      <c r="BE10" s="99">
+        <v>1</v>
+      </c>
       <c r="BF10" s="99"/>
       <c r="BG10" s="99"/>
       <c r="BH10" s="99"/>
@@ -3818,9 +3798,11 @@
         <v>1</v>
       </c>
       <c r="BD11" s="99">
-        <v>0.95</v>
-      </c>
-      <c r="BE11" s="99"/>
+        <v>1</v>
+      </c>
+      <c r="BE11" s="99">
+        <v>1</v>
+      </c>
       <c r="BF11" s="99"/>
       <c r="BG11" s="99"/>
       <c r="BH11" s="99"/>
@@ -3912,9 +3894,11 @@
         <v>0.8</v>
       </c>
       <c r="BD12" s="99">
-        <v>0.95</v>
-      </c>
-      <c r="BE12" s="98"/>
+        <v>1</v>
+      </c>
+      <c r="BE12" s="99">
+        <v>1</v>
+      </c>
       <c r="BF12" s="98"/>
       <c r="BG12" s="98"/>
       <c r="BH12" s="98"/>
@@ -4109,9 +4093,9 @@
       <c r="Y15" s="71"/>
       <c r="Z15" s="86"/>
       <c r="AA15" s="134"/>
-      <c r="AB15" s="136"/>
-      <c r="AC15" s="136"/>
-      <c r="AD15" s="136"/>
+      <c r="AB15" s="134"/>
+      <c r="AC15" s="134"/>
+      <c r="AD15" s="134"/>
       <c r="AE15" s="71"/>
       <c r="AF15" s="71"/>
       <c r="AG15" s="137"/>
@@ -4146,9 +4130,11 @@
         <v>0.15</v>
       </c>
       <c r="BD15" s="99">
-        <v>0.25</v>
-      </c>
-      <c r="BE15" s="98"/>
+        <v>0.3</v>
+      </c>
+      <c r="BE15" s="99">
+        <v>0.7</v>
+      </c>
       <c r="BF15" s="98"/>
       <c r="BG15" s="98"/>
       <c r="BH15" s="98"/>
@@ -4291,9 +4277,7 @@
       <c r="AG17" s="85"/>
       <c r="AH17" s="77"/>
       <c r="AI17" s="71"/>
-      <c r="AJ17" s="145" t="s">
-        <v>43</v>
-      </c>
+      <c r="AJ17" s="71"/>
       <c r="AK17" s="71"/>
       <c r="AL17" s="71"/>
       <c r="AM17" s="71"/>
@@ -4504,7 +4488,9 @@
       <c r="AA24" s="104"/>
       <c r="AB24" s="104"/>
       <c r="AC24" s="104"/>
-      <c r="AD24" s="104"/>
+      <c r="AD24" s="130" t="s">
+        <v>38</v>
+      </c>
       <c r="AE24" s="105"/>
       <c r="AF24" s="105"/>
       <c r="AG24" s="104"/>
@@ -4763,7 +4749,7 @@
     <mergeCell ref="AA5:AG5"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
-  <conditionalFormatting sqref="F6:AU16 F18:AU18 F17:AI17 AK17:AU17">
+  <conditionalFormatting sqref="F6:AU18">
     <cfRule type="expression" dxfId="18" priority="25">
       <formula>WEEKDAY(F$6,2)=6</formula>
     </cfRule>
@@ -4841,7 +4827,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>F6:AU16 F18:AU18 F17:AI17 AK17:AU17</xm:sqref>
+          <xm:sqref>F6:AU18</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="23" id="{274BD6AE-E775-4CB0-A081-F947D5D49C44}">
@@ -5050,26 +5036,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5357,6 +5323,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5367,25 +5353,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5406,6 +5373,25 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>

--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E53FBF-3197-4805-B086-48000F6CF142}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B71428F-1F1B-44E6-A45E-42C4CC1B0555}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13755" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="42">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -3207,10 +3207,14 @@
         <v>46296</v>
       </c>
       <c r="BE6" s="102">
-        <v>46267</v>
-      </c>
-      <c r="BF6" s="102"/>
-      <c r="BG6" s="102"/>
+        <v>46297</v>
+      </c>
+      <c r="BF6" s="102">
+        <v>46300</v>
+      </c>
+      <c r="BG6" s="102">
+        <v>46301</v>
+      </c>
       <c r="BH6" s="102"/>
       <c r="BI6" s="102"/>
       <c r="BJ6" s="102"/>
@@ -3703,8 +3707,12 @@
       <c r="BE10" s="99">
         <v>1</v>
       </c>
-      <c r="BF10" s="99"/>
-      <c r="BG10" s="99"/>
+      <c r="BF10" s="99">
+        <v>1</v>
+      </c>
+      <c r="BG10" s="99">
+        <v>1</v>
+      </c>
       <c r="BH10" s="99"/>
       <c r="BI10" s="99"/>
       <c r="BJ10" s="99"/>
@@ -3803,8 +3811,12 @@
       <c r="BE11" s="99">
         <v>1</v>
       </c>
-      <c r="BF11" s="99"/>
-      <c r="BG11" s="99"/>
+      <c r="BF11" s="99">
+        <v>1</v>
+      </c>
+      <c r="BG11" s="99">
+        <v>1</v>
+      </c>
       <c r="BH11" s="99"/>
       <c r="BI11" s="99"/>
       <c r="BJ11" s="99"/>
@@ -3899,8 +3911,12 @@
       <c r="BE12" s="99">
         <v>1</v>
       </c>
-      <c r="BF12" s="98"/>
-      <c r="BG12" s="98"/>
+      <c r="BF12" s="99">
+        <v>1</v>
+      </c>
+      <c r="BG12" s="99">
+        <v>1</v>
+      </c>
       <c r="BH12" s="98"/>
       <c r="BI12" s="98"/>
       <c r="BJ12" s="98"/>
@@ -4122,10 +4138,18 @@
       <c r="AX15" s="99">
         <v>0</v>
       </c>
-      <c r="AY15" s="98"/>
-      <c r="AZ15" s="98"/>
-      <c r="BA15" s="98"/>
-      <c r="BB15" s="98"/>
+      <c r="AY15" s="99">
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="99">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="99">
+        <v>0</v>
+      </c>
+      <c r="BB15" s="99">
+        <v>0</v>
+      </c>
       <c r="BC15" s="99">
         <v>0.15</v>
       </c>
@@ -4135,8 +4159,12 @@
       <c r="BE15" s="99">
         <v>0.7</v>
       </c>
-      <c r="BF15" s="98"/>
-      <c r="BG15" s="98"/>
+      <c r="BF15" s="99">
+        <v>0.85</v>
+      </c>
+      <c r="BG15" s="99">
+        <v>0.9</v>
+      </c>
       <c r="BH15" s="98"/>
       <c r="BI15" s="98"/>
       <c r="BJ15" s="98"/>
@@ -4212,17 +4240,33 @@
       <c r="AX16" s="99">
         <v>0</v>
       </c>
-      <c r="AY16" s="98"/>
-      <c r="AZ16" s="98"/>
-      <c r="BA16" s="98"/>
-      <c r="BB16" s="98"/>
-      <c r="BC16" s="98"/>
+      <c r="AY16" s="99">
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="99">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="99">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="99">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="99">
+        <v>0</v>
+      </c>
       <c r="BD16" s="99">
         <v>0</v>
       </c>
-      <c r="BE16" s="98"/>
-      <c r="BF16" s="98"/>
-      <c r="BG16" s="98"/>
+      <c r="BE16" s="99">
+        <v>0</v>
+      </c>
+      <c r="BF16" s="99">
+        <v>0</v>
+      </c>
+      <c r="BG16" s="99">
+        <v>0</v>
+      </c>
       <c r="BH16" s="98"/>
       <c r="BI16" s="98"/>
       <c r="BJ16" s="98"/>
@@ -4298,17 +4342,33 @@
       <c r="AX17" s="99">
         <v>0</v>
       </c>
-      <c r="AY17" s="98"/>
-      <c r="AZ17" s="98"/>
-      <c r="BA17" s="98"/>
-      <c r="BB17" s="98"/>
-      <c r="BC17" s="98"/>
+      <c r="AY17" s="99">
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="99">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="99">
+        <v>0</v>
+      </c>
+      <c r="BB17" s="99">
+        <v>0</v>
+      </c>
+      <c r="BC17" s="99">
+        <v>0</v>
+      </c>
       <c r="BD17" s="99">
         <v>0</v>
       </c>
-      <c r="BE17" s="98"/>
-      <c r="BF17" s="98"/>
-      <c r="BG17" s="98"/>
+      <c r="BE17" s="99">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="99">
+        <v>0</v>
+      </c>
+      <c r="BG17" s="99">
+        <v>0</v>
+      </c>
       <c r="BH17" s="98"/>
       <c r="BI17" s="98"/>
       <c r="BJ17" s="98"/>
@@ -4501,10 +4561,18 @@
       <c r="AL24" s="105"/>
       <c r="AM24" s="105"/>
       <c r="AN24" s="105"/>
-      <c r="AO24" s="104"/>
-      <c r="AP24" s="104"/>
-      <c r="AQ24" s="104"/>
-      <c r="AR24" s="104"/>
+      <c r="AO24" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP24" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ24" s="108" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR24" s="108" t="s">
+        <v>27</v>
+      </c>
       <c r="AS24" s="105"/>
       <c r="AT24" s="105"/>
       <c r="AU24" s="104"/>
@@ -5036,6 +5104,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5323,7 +5400,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -5343,16 +5420,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5373,29 +5449,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B71428F-1F1B-44E6-A45E-42C4CC1B0555}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CC82AE-4975-4B35-9721-6D060D06448B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13755" windowHeight="10035" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="11" r:id="rId1"/>
@@ -3215,8 +3215,12 @@
       <c r="BG6" s="102">
         <v>46301</v>
       </c>
-      <c r="BH6" s="102"/>
-      <c r="BI6" s="102"/>
+      <c r="BH6" s="102">
+        <v>46302</v>
+      </c>
+      <c r="BI6" s="102">
+        <v>46303</v>
+      </c>
       <c r="BJ6" s="102"/>
       <c r="BK6" s="102"/>
       <c r="BL6" s="102"/>
@@ -3713,8 +3717,12 @@
       <c r="BG10" s="99">
         <v>1</v>
       </c>
-      <c r="BH10" s="99"/>
-      <c r="BI10" s="99"/>
+      <c r="BH10" s="99">
+        <v>1</v>
+      </c>
+      <c r="BI10" s="99">
+        <v>1</v>
+      </c>
       <c r="BJ10" s="99"/>
       <c r="BK10" s="99"/>
       <c r="BL10" s="99"/>
@@ -3817,8 +3825,12 @@
       <c r="BG11" s="99">
         <v>1</v>
       </c>
-      <c r="BH11" s="99"/>
-      <c r="BI11" s="99"/>
+      <c r="BH11" s="99">
+        <v>1</v>
+      </c>
+      <c r="BI11" s="99">
+        <v>1</v>
+      </c>
       <c r="BJ11" s="99"/>
       <c r="BK11" s="99"/>
       <c r="BL11" s="99"/>
@@ -3917,8 +3929,12 @@
       <c r="BG12" s="99">
         <v>1</v>
       </c>
-      <c r="BH12" s="98"/>
-      <c r="BI12" s="98"/>
+      <c r="BH12" s="99">
+        <v>1</v>
+      </c>
+      <c r="BI12" s="99">
+        <v>1</v>
+      </c>
       <c r="BJ12" s="98"/>
       <c r="BK12" s="98"/>
       <c r="BL12" s="98"/>
@@ -4165,8 +4181,12 @@
       <c r="BG15" s="99">
         <v>0.9</v>
       </c>
-      <c r="BH15" s="98"/>
-      <c r="BI15" s="98"/>
+      <c r="BH15" s="99">
+        <v>0.9</v>
+      </c>
+      <c r="BI15" s="99">
+        <v>1</v>
+      </c>
       <c r="BJ15" s="98"/>
       <c r="BK15" s="98"/>
       <c r="BL15" s="98"/>
@@ -4267,8 +4287,12 @@
       <c r="BG16" s="99">
         <v>0</v>
       </c>
-      <c r="BH16" s="98"/>
-      <c r="BI16" s="98"/>
+      <c r="BH16" s="99">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="99">
+        <v>0</v>
+      </c>
       <c r="BJ16" s="98"/>
       <c r="BK16" s="98"/>
       <c r="BL16" s="98"/>
@@ -4369,8 +4393,12 @@
       <c r="BG17" s="99">
         <v>0</v>
       </c>
-      <c r="BH17" s="98"/>
-      <c r="BI17" s="98"/>
+      <c r="BH17" s="99">
+        <v>0</v>
+      </c>
+      <c r="BI17" s="99">
+        <v>0</v>
+      </c>
       <c r="BJ17" s="98"/>
       <c r="BK17" s="98"/>
       <c r="BL17" s="98"/>
@@ -5104,15 +5132,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5400,6 +5419,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5421,14 +5449,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5449,21 +5469,29 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CC82AE-4975-4B35-9721-6D060D06448B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCA859E-7C2E-4EFA-A084-4F1F11971B4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="43">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -318,6 +318,13 @@
     <t>全員</t>
     <rPh sb="0" eb="2">
       <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>欠席</t>
+    <rPh sb="0" eb="2">
+      <t>ケッセキ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -880,7 +887,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -1692,6 +1699,21 @@
       </left>
       <right style="thin">
         <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC0C0C0"/>
       </right>
       <top style="dotted">
         <color theme="0" tint="-0.24994659260841701"/>
@@ -1773,7 +1795,7 @@
     <xf numFmtId="0" fontId="1" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2164,6 +2186,21 @@
     </xf>
     <xf numFmtId="179" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2531,8 +2568,8 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFC0C0C0"/>
       <color rgb="FFFFFF66"/>
-      <color rgb="FFC0C0C0"/>
       <color rgb="FF969696"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFFFFFCC"/>
@@ -2830,7 +2867,9 @@
     <col min="5" max="5" width="12.6640625" style="6" customWidth="1"/>
     <col min="6" max="47" width="5.21875" style="6" customWidth="1"/>
     <col min="48" max="48" width="11.77734375" style="6" customWidth="1"/>
-    <col min="49" max="68" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="49" max="61" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="64" max="68" width="11.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="69" max="16384" width="8.77734375" style="6"/>
   </cols>
   <sheetData>
@@ -3221,8 +3260,12 @@
       <c r="BI6" s="102">
         <v>46303</v>
       </c>
-      <c r="BJ6" s="102"/>
-      <c r="BK6" s="102"/>
+      <c r="BJ6" s="102">
+        <v>46308</v>
+      </c>
+      <c r="BK6" s="102">
+        <v>46309</v>
+      </c>
       <c r="BL6" s="102"/>
       <c r="BM6" s="102"/>
       <c r="BN6" s="102"/>
@@ -3723,7 +3766,9 @@
       <c r="BI10" s="99">
         <v>1</v>
       </c>
-      <c r="BJ10" s="99"/>
+      <c r="BJ10" s="99">
+        <v>1</v>
+      </c>
       <c r="BK10" s="99"/>
       <c r="BL10" s="99"/>
       <c r="BM10" s="99"/>
@@ -3831,7 +3876,9 @@
       <c r="BI11" s="99">
         <v>1</v>
       </c>
-      <c r="BJ11" s="99"/>
+      <c r="BJ11" s="99">
+        <v>1</v>
+      </c>
       <c r="BK11" s="99"/>
       <c r="BL11" s="99"/>
       <c r="BM11" s="99"/>
@@ -3873,8 +3920,8 @@
       <c r="W12" s="112"/>
       <c r="X12" s="77"/>
       <c r="Y12" s="86"/>
-      <c r="Z12" s="112"/>
-      <c r="AA12" s="77"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="70"/>
       <c r="AB12" s="71"/>
       <c r="AC12" s="71"/>
       <c r="AD12" s="71"/>
@@ -3935,7 +3982,9 @@
       <c r="BI12" s="99">
         <v>1</v>
       </c>
-      <c r="BJ12" s="98"/>
+      <c r="BJ12" s="99">
+        <v>1</v>
+      </c>
       <c r="BK12" s="98"/>
       <c r="BL12" s="98"/>
       <c r="BM12" s="98"/>
@@ -4124,21 +4173,21 @@
       <c r="X15" s="71"/>
       <c r="Y15" s="71"/>
       <c r="Z15" s="86"/>
-      <c r="AA15" s="134"/>
-      <c r="AB15" s="134"/>
-      <c r="AC15" s="134"/>
-      <c r="AD15" s="134"/>
+      <c r="AA15" s="146"/>
+      <c r="AB15" s="147"/>
+      <c r="AC15" s="147"/>
+      <c r="AD15" s="148"/>
       <c r="AE15" s="71"/>
       <c r="AF15" s="71"/>
       <c r="AG15" s="137"/>
       <c r="AH15" s="138"/>
       <c r="AI15" s="136"/>
-      <c r="AJ15" s="71"/>
+      <c r="AJ15" s="136"/>
       <c r="AK15" s="71"/>
       <c r="AL15" s="71"/>
       <c r="AM15" s="71"/>
       <c r="AN15" s="86"/>
-      <c r="AO15" s="70"/>
+      <c r="AO15" s="134"/>
       <c r="AP15" s="71"/>
       <c r="AQ15" s="71"/>
       <c r="AR15" s="71"/>
@@ -4187,7 +4236,9 @@
       <c r="BI15" s="99">
         <v>1</v>
       </c>
-      <c r="BJ15" s="98"/>
+      <c r="BJ15" s="99">
+        <v>1</v>
+      </c>
       <c r="BK15" s="98"/>
       <c r="BL15" s="98"/>
       <c r="BM15" s="98"/>
@@ -4239,13 +4290,13 @@
       <c r="AG16" s="85"/>
       <c r="AH16" s="77"/>
       <c r="AI16" s="71"/>
-      <c r="AJ16" s="71"/>
+      <c r="AJ16" s="136"/>
       <c r="AK16" s="71"/>
       <c r="AL16" s="71"/>
       <c r="AM16" s="71"/>
       <c r="AN16" s="86"/>
-      <c r="AO16" s="70"/>
-      <c r="AP16" s="71"/>
+      <c r="AO16" s="145"/>
+      <c r="AP16" s="136"/>
       <c r="AQ16" s="71"/>
       <c r="AR16" s="71"/>
       <c r="AS16" s="71"/>
@@ -4293,7 +4344,9 @@
       <c r="BI16" s="99">
         <v>0</v>
       </c>
-      <c r="BJ16" s="98"/>
+      <c r="BJ16" s="99">
+        <v>0.9</v>
+      </c>
       <c r="BK16" s="98"/>
       <c r="BL16" s="98"/>
       <c r="BM16" s="98"/>
@@ -4352,7 +4405,7 @@
       <c r="AN17" s="86"/>
       <c r="AO17" s="70"/>
       <c r="AP17" s="71"/>
-      <c r="AQ17" s="71"/>
+      <c r="AQ17" s="136"/>
       <c r="AR17" s="71"/>
       <c r="AS17" s="71"/>
       <c r="AT17" s="71"/>
@@ -4399,7 +4452,9 @@
       <c r="BI17" s="99">
         <v>0</v>
       </c>
-      <c r="BJ17" s="98"/>
+      <c r="BJ17" s="99">
+        <v>0</v>
+      </c>
       <c r="BK17" s="98"/>
       <c r="BL17" s="98"/>
       <c r="BM17" s="98"/>
@@ -4769,7 +4824,7 @@
       <c r="AG27" s="104"/>
       <c r="AH27" s="104"/>
       <c r="AI27" s="104"/>
-      <c r="AJ27" s="104"/>
+      <c r="AJ27" s="149"/>
       <c r="AK27" s="105"/>
       <c r="AL27" s="105"/>
       <c r="AM27" s="105"/>
@@ -4825,7 +4880,9 @@
       <c r="AL28" s="105"/>
       <c r="AM28" s="105"/>
       <c r="AN28" s="105"/>
-      <c r="AO28" s="104"/>
+      <c r="AO28" s="130" t="s">
+        <v>42</v>
+      </c>
       <c r="AP28" s="104"/>
       <c r="AQ28" s="104"/>
       <c r="AR28" s="104"/>
@@ -5132,6 +5189,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5419,36 +5505,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5467,31 +5551,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/アプリケーション企画実習/進捗管理.xlsx
+++ b/アプリケーション企画実習/進捗管理.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCA859E-7C2E-4EFA-A084-4F1F11971B4C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC2ECF6-1319-40C8-B9BD-8A9E72D69311}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="44">
   <si>
     <t>セル B2 には会社の名前を入力します。</t>
   </si>
@@ -318,6 +318,13 @@
     <t>全員</t>
     <rPh sb="0" eb="2">
       <t>ゼンイン</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>欠席</t>
+    <rPh sb="0" eb="2">
+      <t>ケッセキ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -2169,6 +2176,21 @@
     <xf numFmtId="0" fontId="24" fillId="48" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="48" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="43" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="27" fillId="39" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -2186,21 +2208,6 @@
     </xf>
     <xf numFmtId="179" fontId="27" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="48" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="43" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2908,8 +2915,8 @@
       </c>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="144"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
     </row>
     <row r="5" spans="1:68" ht="25.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -2921,66 +2928,66 @@
       <c r="C5" s="15"/>
       <c r="D5" s="55"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="139">
+      <c r="F5" s="144">
         <f>D10</f>
         <v>46273</v>
       </c>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="141"/>
-      <c r="M5" s="139">
+      <c r="G5" s="145"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="145"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="144">
         <f>M6</f>
         <v>46280</v>
       </c>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="140"/>
-      <c r="S5" s="141"/>
-      <c r="T5" s="142">
+      <c r="N5" s="145"/>
+      <c r="O5" s="145"/>
+      <c r="P5" s="145"/>
+      <c r="Q5" s="145"/>
+      <c r="R5" s="145"/>
+      <c r="S5" s="146"/>
+      <c r="T5" s="147">
         <f>T6</f>
         <v>46287</v>
       </c>
-      <c r="U5" s="140"/>
-      <c r="V5" s="140"/>
-      <c r="W5" s="140"/>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="140"/>
-      <c r="Z5" s="143"/>
-      <c r="AA5" s="139">
+      <c r="U5" s="145"/>
+      <c r="V5" s="145"/>
+      <c r="W5" s="145"/>
+      <c r="X5" s="145"/>
+      <c r="Y5" s="145"/>
+      <c r="Z5" s="148"/>
+      <c r="AA5" s="144">
         <f>AA6</f>
         <v>46294</v>
       </c>
-      <c r="AB5" s="140"/>
-      <c r="AC5" s="140"/>
-      <c r="AD5" s="140"/>
-      <c r="AE5" s="140"/>
-      <c r="AF5" s="140"/>
-      <c r="AG5" s="141"/>
-      <c r="AH5" s="142">
+      <c r="AB5" s="145"/>
+      <c r="AC5" s="145"/>
+      <c r="AD5" s="145"/>
+      <c r="AE5" s="145"/>
+      <c r="AF5" s="145"/>
+      <c r="AG5" s="146"/>
+      <c r="AH5" s="147">
         <f>AH6</f>
         <v>46301</v>
       </c>
-      <c r="AI5" s="140"/>
-      <c r="AJ5" s="140"/>
-      <c r="AK5" s="140"/>
-      <c r="AL5" s="140"/>
-      <c r="AM5" s="140"/>
-      <c r="AN5" s="143"/>
-      <c r="AO5" s="139">
+      <c r="AI5" s="145"/>
+      <c r="AJ5" s="145"/>
+      <c r="AK5" s="145"/>
+      <c r="AL5" s="145"/>
+      <c r="AM5" s="145"/>
+      <c r="AN5" s="148"/>
+      <c r="AO5" s="144">
         <f>AO6</f>
         <v>46308</v>
       </c>
-      <c r="AP5" s="140"/>
-      <c r="AQ5" s="140"/>
-      <c r="AR5" s="140"/>
-      <c r="AS5" s="140"/>
-      <c r="AT5" s="140"/>
-      <c r="AU5" s="141"/>
+      <c r="AP5" s="145"/>
+      <c r="AQ5" s="145"/>
+      <c r="AR5" s="145"/>
+      <c r="AS5" s="145"/>
+      <c r="AT5" s="145"/>
+      <c r="AU5" s="146"/>
       <c r="AV5" s="101" t="s">
         <v>24</v>
       </c>
@@ -3769,7 +3776,9 @@
       <c r="BJ10" s="99">
         <v>1</v>
       </c>
-      <c r="BK10" s="99"/>
+      <c r="BK10" s="99">
+        <v>1</v>
+      </c>
       <c r="BL10" s="99"/>
       <c r="BM10" s="99"/>
       <c r="BN10" s="99"/>
@@ -3879,7 +3888,9 @@
       <c r="BJ11" s="99">
         <v>1</v>
       </c>
-      <c r="BK11" s="99"/>
+      <c r="BK11" s="99">
+        <v>1</v>
+      </c>
       <c r="BL11" s="99"/>
       <c r="BM11" s="99"/>
       <c r="BN11" s="99"/>
@@ -3985,7 +3996,9 @@
       <c r="BJ12" s="99">
         <v>1</v>
       </c>
-      <c r="BK12" s="98"/>
+      <c r="BK12" s="99">
+        <v>1</v>
+      </c>
       <c r="BL12" s="98"/>
       <c r="BM12" s="98"/>
       <c r="BN12" s="98"/>
@@ -4057,7 +4070,7 @@
       <c r="BH13" s="98"/>
       <c r="BI13" s="98"/>
       <c r="BJ13" s="98"/>
-      <c r="BK13" s="98"/>
+      <c r="BK13" s="99"/>
       <c r="BL13" s="98"/>
       <c r="BM13" s="98"/>
       <c r="BN13" s="98"/>
@@ -4131,7 +4144,7 @@
       <c r="BH14" s="98"/>
       <c r="BI14" s="98"/>
       <c r="BJ14" s="98"/>
-      <c r="BK14" s="98"/>
+      <c r="BK14" s="99"/>
       <c r="BL14" s="98"/>
       <c r="BM14" s="98"/>
       <c r="BN14" s="98"/>
@@ -4173,10 +4186,10 @@
       <c r="X15" s="71"/>
       <c r="Y15" s="71"/>
       <c r="Z15" s="86"/>
-      <c r="AA15" s="146"/>
-      <c r="AB15" s="147"/>
-      <c r="AC15" s="147"/>
-      <c r="AD15" s="148"/>
+      <c r="AA15" s="140"/>
+      <c r="AB15" s="141"/>
+      <c r="AC15" s="141"/>
+      <c r="AD15" s="142"/>
       <c r="AE15" s="71"/>
       <c r="AF15" s="71"/>
       <c r="AG15" s="137"/>
@@ -4239,7 +4252,9 @@
       <c r="BJ15" s="99">
         <v>1</v>
       </c>
-      <c r="BK15" s="98"/>
+      <c r="BK15" s="99">
+        <v>1</v>
+      </c>
       <c r="BL15" s="98"/>
       <c r="BM15" s="98"/>
       <c r="BN15" s="98"/>
@@ -4295,8 +4310,8 @@
       <c r="AL16" s="71"/>
       <c r="AM16" s="71"/>
       <c r="AN16" s="86"/>
-      <c r="AO16" s="145"/>
-      <c r="AP16" s="136"/>
+      <c r="AO16" s="139"/>
+      <c r="AP16" s="112"/>
       <c r="AQ16" s="71"/>
       <c r="AR16" s="71"/>
       <c r="AS16" s="71"/>
@@ -4347,7 +4362,9 @@
       <c r="BJ16" s="99">
         <v>0.9</v>
       </c>
-      <c r="BK16" s="98"/>
+      <c r="BK16" s="99">
+        <v>1</v>
+      </c>
       <c r="BL16" s="98"/>
       <c r="BM16" s="98"/>
       <c r="BN16" s="98"/>
@@ -4455,7 +4472,7 @@
       <c r="BJ17" s="99">
         <v>0</v>
       </c>
-      <c r="BK17" s="98"/>
+      <c r="BK17" s="99"/>
       <c r="BL17" s="98"/>
       <c r="BM17" s="98"/>
       <c r="BN17" s="98"/>
@@ -4824,7 +4841,7 @@
       <c r="AG27" s="104"/>
       <c r="AH27" s="104"/>
       <c r="AI27" s="104"/>
-      <c r="AJ27" s="149"/>
+      <c r="AJ27" s="143"/>
       <c r="AK27" s="105"/>
       <c r="AL27" s="105"/>
       <c r="AM27" s="105"/>
@@ -4883,7 +4900,9 @@
       <c r="AO28" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="AP28" s="104"/>
+      <c r="AP28" s="130" t="s">
+        <v>43</v>
+      </c>
       <c r="AQ28" s="104"/>
       <c r="AR28" s="104"/>
       <c r="AS28" s="105"/>
@@ -5189,35 +5208,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5505,34 +5495,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5551,4 +5543,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>